--- a/ably/assets/ably-performance-ad-prd.xlsx
+++ b/ably/assets/ably-performance-ad-prd.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
   <si>
     <t>에이블리 입점 중소·신규 셀러를 위한 순수 성과형 상품광고</t>
   </si>
@@ -92,6 +92,7 @@
 건전성  공짜 소진율  15% 이하  10% 이하  20% 초과
 건전성  전환 예측 오차  절대오차 20% 이하  15% 이하  30% 초과
 건전성  유효 전환율  0.15% 이상  0.18% 이상  0.12% 미만
+신규 한정과 성과형 월 집행 상한은 eCPM 동일 경매, oCPM 바닥가 가드레일과 함께 기존 oCPM 매출 잠식을 막는 1차 장치로 운영한다. 지면 매출 유지율 95% 이상은 이 장치가 작동하는지 검증하는 핵심 지표이며, 관련 수치와 임계값은 모두 파일럿 가정으로 운영 데이터에 따라 보정한다.
 수익 임팩트는 파일럿 지면의 월 1,000만 회 노출, 기존 oCPM 5,000원, 구매 전환 단가 4,000원, 평균 주문금액 40,000원, 거래 수수료율 7%, 광고 변동비 15%를 공통 가정으로 산정한다. 성과형 광고 기여 GMV는 oCPM으로는 유입되지 않던 신규 셀러가 만드는 증분 구매 GMV로 정의하며, 자연전환과 기존 oCPM 베이스라인에 포함된 GMV는 제외한다. 따라서 이 GMV에서 발생하는 거래 수수료는 기존 oCPM 베이스라인에 없던 순증분 기여로 계산한다. 파일럿에서는 대조군 기반 증분성 검증으로 이를 재산정한다. 이 비교는 지면 전체를 성과형으로 대체하는 경우가 아니라 성과형에 배정된 인벤토리 단위 기준이며, 전체 지면에서 성과형 매출 비중은 파일럿 5%와 확대 단계 10%를 목표로 한다.
 평가 기준은 광고 매출이 아니라 ‘에이블리 총 기여=광고비+광고 기여 GMV×거래 수수료율’로 둔다. 전환 1건당 거래 수수료 기여는 40,000원×7%=2,800원이며, 기존 oCPM 비교 기준은 광고 매출 5,000만원과 광고 변동비 차감 이익 4,250만원이다.
 시나리오  유효 전환율  공짜 소진율  광고비  광고 기여 GMV  거래 수수료  에이블리 총 기여  기존 oCPM 대비 총 기여 변화  총 기여 이익보수  0.11%  18%  3,608만원  4억 4,000만원  3,080만원  6,688만원  +34%  6,147만원
@@ -104,7 +105,7 @@
     <t>리스크</t>
   </si>
   <si>
-    <t>첫째, 전환이 발생하지 않는 상품이 상품광고 지면을 점유해 플랫폼이 무료 노출과 인벤토리 기회비용을 부담할 수 있다. 성과형 캠페인을 예상 전환율×전환 단가의 eCPM으로 환산해 oCPM과 동일 경매에서 경쟁시키고, 예상 eCPM이 지면별 oCPM 바닥가의 95% 미만이면 자동으로 우선순위를 낮추며 80% 미만이면 oCPM 캠페인으로 대체한다. 둘째, 전환 가능성이 낮은 광고주가 성과형 상품에 몰리는 역선택을 막기 위해 과거 판매량·평점·재고·배송 품질·카테고리 전환율로 참여 자격과 셀러당 일일 노출 한도를 제한한다. 셋째, 셀프 구매·쿠폰 반복 사용 등 가짜 전환은 결제자·기기·계정 중복 제거, 환불·취소 제외, 이상 패턴 탐지, 전환 검증 보류 및 정산 조정으로 방어한다. 넷째, 자연적으로 구매할 고객에게도 광고 기여를 인정하면 광고비와 거래 수수료의 증분 기여를 과대평가할 수 있으므로 클릭 후 기여 윈도우, 중복 제거, 자연전환과 광고 기여전환 구분 및 대조군 기반 증분성 분석을 적용한다. 다섯째, 성과형 상품이 기존 CPD 매출을 잠식할 수 있으므로 대형 브랜드 CPD는 유지하고 MVP를 중소·신규 셀러와 한정 지면에 제한한다. 여섯째, 외부 미입점 광고주는 거래 수수료가 발생하지 않아 순수 광고 수익과 인벤토리 수익성만으로 손익을 검증해야 하므로 입점 셀러 파일럿 이후 Phase 2에서 별도 기준으로 검토한다.</t>
+    <t>첫째, 전환이 발생하지 않는 상품이 상품광고 지면을 점유해 플랫폼이 무료 노출과 인벤토리 기회비용을 부담할 수 있다. 성과형 캠페인을 예상 전환율×전환 단가의 eCPM으로 환산해 oCPM과 동일 경매에서 경쟁시키고, 예상 eCPM이 지면별 oCPM 바닥가의 95% 미만이면 자동으로 우선순위를 낮추며 80% 미만이면 oCPM 캠페인으로 대체한다. 둘째, 전환 가능성이 낮은 광고주가 성과형 상품에 몰리는 역선택을 막기 위해 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주만 MVP 참여 대상으로 제한하고, 기존 품질 게이트와 성과형 월 집행 상한을 함께 적용한다. 이 신규 한정·집행 상한은 eCPM 동일 경매·바닥가 가드레일·지면 매출 유지율 95%와 함께 기존 oCPM 매출 잠식을 막는 1차 장치다. 셋째, 셀프 구매·쿠폰 반복 사용 등 가짜 전환은 결제자·기기·계정 중복 제거, 환불·취소 제외, 이상 패턴 탐지, 전환 검증 보류 및 정산 조정으로 방어한다. 넷째, 자연적으로 구매할 고객에게도 광고 기여를 인정하면 광고비와 거래 수수료의 증분 기여를 과대평가할 수 있으므로 클릭 후 기여 윈도우, 중복 제거, 자연전환과 광고 기여전환 구분 및 대조군 기반 증분성 분석을 적용한다. 다섯째, 성과형 상품이 기존 CPD·oCPM 매출을 잠식할 수 있으므로 대형 브랜드 CPD는 유지하고 MVP를 신규 중소 셀러와 한정 지면에 제한하며, 유효 전환 50건 달성 셀러에게는 oCPM 유상 광고 전환을 안내한다. 여섯째, Phase 2에서 소액 기존 중소 셀러로 확대할 때는 내부 머신러닝 학습 안정성과 운영 데이터를 기준으로 졸업 기준 상향을 검토하고, eCPM 경매와 집행 상한으로 잠식을 계속 방어한다. 일곱째, 외부 미입점 광고주는 거래 수수료가 발생하지 않아 순수 광고 수익과 인벤토리 수익성만으로 손익을 검증해야 하므로 입점 셀러 파일럿 이후 Phase 2에서 별도 기준으로 검토한다.</t>
   </si>
   <si>
     <t>카테고리</t>
@@ -161,7 +162,7 @@
     <t xml:space="preserve">입점 중소·신규 셀러가 기존 활성 광고 지면에 캠페인을 생성하고, 구매·쿠폰 사용·앱 설치 등 유효 전환이 발생한 경우에만 전환 단가 기준으로 비용을 지불하도록 한다. 광고 노출이나 클릭만 발생하고 전환이 없으면 과금하지 않는다. MVP에서는 신규 지면을 개발하지 않고 투데이 추천상품, 투데이·검색결과 유사 상품 추천, 상품상세 연관추천, 검색 기반 신규 지면에 과금 레이어를 적용한다. CPA 상한 보장과 전환 건수 보장은 Phase 2로 제외한다.
 1. ○ Given 참여 자격을 충족한 입점 셀러가 상품과 전환 유형을 선택했을 때, When 일일 또는 총예산과 기간을 입력해 검토를 요청하면, Then 플랫폼은 적용 전환 단가·예상 전환 수·예상 비용을 표시하고 초안 캠페인을 저장한다.
 2. ○ Given 심사를 통과한 캠페인이 집행 중일 때, When 노출 또는 클릭만 발생하면, Then 캠페인 비용은 0원으로 유지된다.
-3. ○ Given 유효 전환이 확정되었을 때, When 전환 비용을 계산하면, Then 확정 전환 수와 사전 고지된 전환 단가만 반영해 비용을 계산한다.
+3. ○ Given 유효 전환이 확정되었을 때, When 누적 유효 전환 수가 50건에 도달하면, Then 성과 검증 완료로 기록하고 oCPM 유상 광고 전환을 안내하며 성과형 월 집행 상한을 적용한다.
 4. ○ Given 캠페인이 예산·노출 한도 또는 참여 제한에 도달했을 때, When 다음 노출 기회가 발생하면, Then 신규 노출을 제한하고 제한 사유를 기록한다.</t>
   </si>
   <si>
@@ -174,7 +175,7 @@
     <t>1.1 성과형 캠페인 생성 및 비용 관리</t>
   </si>
   <si>
-    <t xml:space="preserve">입점 셀러가 참여 가능한 상품으로 순수 성과형 상품광고 캠페인을 만들고 예산·기간·전환 유형을 관리하는 기능이다. 유효 전환이 확정된 경우에만 비용을 누적하며, 노출·클릭만으로는 비용을 청구하지 않는다. CPA 상한 보장과 전환 건수 보장은 Phase 2 범위로 제외한다.
+    <t xml:space="preserve">최근 N개월 유상 광고 집행 이력이 없는 입점 셀러가 참여 가능한 상품으로 순수 성과형 상품광고 캠페인을 만들고 예산·기간·전환 유형을 관리하는 기능이다. 유효 전환이 확정된 경우에만 비용을 누적하며, 노출·클릭만으로는 비용을 청구하지 않는다. 누적 유효 전환 50건을 달성한 셀러에게는 oCPM 유상 광고 전환을 안내하되 성과형 이용은 월 집행 상한 안에서 유지한다.
 [기능의 근거] 선불 광고비와 성과 불확실성 때문에 상품광고를 시작하기 어려운 중소·신규 셀러가 성과 발생분만 비용을 내도록 지원한다.
 [성공 기준] 첫 캠페인 전환 발생률이 파일럿에서 35% 이상에 도달한다.
 [개발 준비 슬롯]
@@ -188,10 +189,12 @@
 • 플랫폼이 카테고리 기준단가와 품질·예측값 및 상품가 구간 수익 가드를 반영한 적용 전환 단가를 80~120% 범위에서 제시한다.
 • 플랫폼이 예상 전환 수와 예상 비용을 계산해 검토 화면에 표시한다.
 • 셀러가 전환 과금·검증·환불 조정 기준에 동의하면 캠페인을 초안 또는 심사 상태로 저장한다.
-• FE는 입력·검토·상태 화면을 만들고 BE는 생성·예산·비용 계산을 처리하며 Data·ML은 예측값을 제공하고 정산은 확정 비용을 청구 대상으로 전달한다.
+• 누적 유효 전환 수가 50건에 도달하면 플랫폼이 성과 검증 완료로 기록하고 oCPM 유상 광고 전환을 안내하며 성과형 이용은 유지한다.
+• FE는 입력·검토·상태 화면을 만들고 BE는 생성·예산·비용·졸업 상태를 처리하며 Data·ML은 예측값을 제공하고 정산은 확정 비용을 청구 대상으로 전달한다.
 • 결과: - 캠페인, 예산, 적용 전환 단가 및 동의 기록을 저장한다.
-• 유효 전환이 확정될 때만 누적 비용과 잔여 예산을 갱신한다.
-• campaigncreated, campaignstarted, budget_limited 이벤트를 기록한다.
+• 유효 전환이 확정될 때만 누적 비용, 잔여 예산 및 누적 유효 전환 수를 갱신한다.
+• 누적 유효 전환 수가 50건에 도달하면 캠페인·셀러 상태를 졸업으로 전이하고 성과형 월 집행 상한을 적용한다.
+• campaigncreated, campaignstarted, budgetlimited, graduationpending, graduatedocpmrecommended 이벤트를 기록한다.
 • 예외: - 동일한 생성 요청이 반복되면 클라이언트 요청 키로 한 건만 생성한다.
 • 예산 소진 중 발생한 전환은 전환 발생 시점의 집행 가능 여부와 확정 규칙을 기준으로 비용을 처리한다.
 • 심사 중 상품이 품절되거나 참여 자격이 상실되면 캠페인을 제한 상태로 전환한다.
@@ -200,15 +203,18 @@
 • 생성 화면은 상품가 구간 또는 카테고리 평균 주문금액에 따른 참여 제한·단가 조정 사유를 표시한다.
 • 비용이 발생하지 않은 노출·클릭은 0원 과금으로 안내한다.
 • 제한 상태에는 제한 사유와 조정 가능한 상품·예산 안내를 표시한다.
+• 누적 유효 전환 수가 졸업 대기 구간에 진입하면 성과 검증 진행 상태와 oCPM 전환 준비 안내를 표시한다.
+• 졸업 상태에는 oCPM 유상 광고 전환 안내와 성과형 월 집행 상한 적용 사실을 표시한다.
 • 권한 &amp; 접근: - 광고주·입점 셀러는 자기 사업자 소유 상품의 캠페인만 생성·수정할 수 있다.
 • 광고 운영자는 운영 권한 범위에서 심사와 제한 처리를 할 수 있다.
 • 비즈니스 규칙: - MVP의 전환 유형은 구매와 쿠폰 사용이며 앱 설치는 해당 캠페인에 한해 별도 승인 후 적용하거나 Phase 2에서 도입한다.
 • MVP의 전환 단가는 광고주 입찰값이 아니라 플랫폼 제시 카테고리 기준단가를 사용한다.
-• 적용 단가는 지면·상품·셀러의 예상 전환율과 품질 점수에 따라 기준단가의 80~120% 범위에서 조정한다.
+• 적용 단가는 지면·상품·셀러의 예상 전환율과 품질 점수에 ��라 기준단가의 80~120% 범위에서 조정한다.
 • 카테고리 평균 주문금액과 수수료 기여가 파일럿 수익 가정에 미달하면 상품가 구간별 전환 단가를 조정하거나 참여를 제한한다.
-• 캠페인은 예산, 셀러당 일일 노출 한도 및 카테고리 참여 제한을 넘겨 집행할 수 없다.
-• 데이터: - 캠페인은 campaignId, sellerId, 상품Id, 전환유형, 상태, 시작·종료일, 일일예산, 총예산, 적용전환단가, 누적비용, 잔여예산을 가진다.
-• 캠페인은 상품가 구간, 카테고리 평균 주문금액, 예상 거래 수수료 기여와 수익 가드 판정값을 가진다.
+• 캠페인은 예산, 셀러당 일일 노출 한도, 카테고리 참여 제한 및 졸업 후 성과형 월 집행 상한을 넘겨 집행할 수 없다.
+• 누적 유효 전환 50건은 성과 검증 완료와 oCPM 유상 광고 전환 안내의 파일럿 기준이며, 내부 머신러닝 최소 학습 전환 기준과 운영 데이터로 보정한다.
+• 데이터: - 캠페인은 campaignId, sellerId, 상품Id, 전환유형, 상태, 시작·종료일, 일일예산, 총예산, 적용전환단가, 누적비용, 잔여예산, 누적유효전환수, 졸업상태, 졸업일시, 성과형월집행상한을 가진다.
+• 캠페인 상태는 신규-성과형, 졸업 대기, 졸업, 초안, 심사, 집행중, 제한, 중단을 포함한다.
 • 캠페인 생성 요청은 requestId를 유일값으로 저장한다.
 • 비용은 원화 정수 금액으로 저장한다.</t>
   </si>
@@ -278,7 +284,7 @@
   </si>
   <si>
     <t xml:space="preserve">상품 카테고리, 가격대, 사용자 행동, 검색·탐색 관심사, 과거 구매 및 전환 데이터를 활용해 광고 타겟을 구성하고 전환 가능성을 예측한다. 전환이 활발한 카테고리와 지면을 우선 제공하며, 저품질 상품·셀러 및 어뷰징 가능성이 높은 캠페인을 제한한다.
-1. ○ Given 셀러와 상품의 과거 판매·평점·재고·배송 품질 데이터가 있을 때, When 참여 자격을 평가하면, Then 파일럿 기준 충족 여부와 제한 사유를 저장한다.
+1. ○ Given 셀러와 상품의 최근 90일 판매·평점·재고·배송 품질 및 유상 광고 집행 이력이 있을 때, When 참여 자격을 평가하면, Then 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주 여부와 기존 품질 기준 충족 여부 및 제한 사유를 저장한다.
 2. ○ Given 집행 가능한 캠페인이 있을 때, When 지면 경매가 발생하면, Then 예상 전환율과 플랫폼 제시 전환 단가를 사용해 eCPM을 계산한다.
 3. ○ Given 예상 eCPM이 지면별 oCPM 바닥가의 95% 미만일 때, When 노출 우선순위를 산정하면, Then 해당 캠페인의 우선순위를 낮춘다.
 4. ○ Given 동일 계정·기기·결제수단의 반복 전환 또는 비정상 패턴이 탐지되었을 때, When 위험도 기준을 초과하면, Then 전환을 검증 보류하거나 캠페인을 제한하고 근거를 기록한다.</t>
@@ -287,17 +293,19 @@
     <t>3.1 참여 자격 평가와 경매 품질 방어</t>
   </si>
   <si>
-    <t xml:space="preserve">셀러·상품 품질, 상품가 구간과 예상 전환율을 평가해 파일럿 참여 자격, 노출 우선순위 및 이상 전환 방어를 결정하는 기능이다. MVP에서는 플랫폼 제시 전환 단가를 사용하고 예상 전환율이 노출 경쟁의 주 변수이며, 카테고리 평균 주문금액과 수수료 기여가 파일럿 수익 가정을 충족하지 않으면 단가 조정 또는 참여 제한을 적용한다. 목표 CPA 입찰은 Phase 2로 분리한다.
+    <t xml:space="preserve">셀러·상품 품질, 유상 광고 집행 이력, 상품가 구간과 예상 전환율을 평가해 파일럿 참여 자격, 노출 우선순위 및 이상 전환 방어를 결정하는 기능이다. MVP에서는 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주만 참여시키고, 기존 품질 게이트를 유지한다. 누적 유효 전환 50건 달성 셀러는 졸업 상태로 전이해 oCPM 전환을 안내하고 성과형 월 집행 상한으로 대형 셀러 유입을 제한한다.
 [기능의 근거] 전환 가능성이 낮은 캠페인의 무료 노출 소진과 기존 oCPM 매출 기회비용을 방어해야 한다.
 [성공 기준] 공짜 소진율을 파일럿에서 15% 이하로 유지한다.
 [개발 준비 슬롯]
 • 선행조건: - 셀러의 최근 90일 주문, 상품 평점, 품절률, 배송 품질 및 정책 위반 이력이 조회 가능하다.
+• 셀러의 최근 N개월 유상 광고 집행 이력이 내부 광고 집행 기준으로 조회 가능하다.
 • 상품·셀러·지면·사용자 맥락별 예상 전환율과 품질 점수가 제공된다.
 • 경매 엔진이 oCPM 바닥가와 캠페인 노출 한도를 조회할 수 있다.
 • 트리거: - 셀러가 참여 자격 심사를 요청한다.
 • 지면 경매 또는 일일 가드레일 평가가 실행된다.
 • 반복 클릭·자기 구매·쿠폰 악용 등 이상 신호가 수신된다.
-• 동작: - 플랫폼이 셀러·상품 데이터와 카테고리 평균 주문금액·예상 거래 수수료 기여를 기준으로 파일럿 참여 적합성과 제한 사유를 산정한다.
+• 동작: - 플랫폼이 셀러·상품 데이터, 유상 광고 집행 이력 및 카테고리 평균 주문금액·예상 거래 수수료 기여를 기준으로 파일럿 참여 적합성과 제한 사유를 산정한다.
+• 플랫폼이 최근 N개월 유상 광고 집행 이력이 0원인 셀러를 신규 광고주로 판정하고, 별도 매출·거래액 증빙 서류는 요구하지 않는다.
 • 플랫폼이 예상 전환율×플랫폼 제시 전환 단가×1,000으로 MVP 경매 eCPM을 계산한다.
 • 플랫폼이 eCPM과 품질 점수로 oCPM 캠페인과 동일 지면의 랭킹을 산정한다.
 • FE는 자격·제한 안내를 표시하고 BE는 평가·한도를 집행하며 Data·ML은 예측·이상 탐지를 제공하고 정산은 보류 전환을 비용에서 제외한다.
@@ -313,12 +321,15 @@
 • 권한 &amp; 접근: - 광고 운영자와 플랫폼 관리자만 자격 기준·노출 한도·품질 제한을 변경할 수 있다.
 • 광고주는 자기 캠페인의 제한 결과와 개선 안내만 조회할 수 있다.
 • 비즈니스 규칙: - MVP의 적용 전환 단가는 카테고리 기준단가의 80~120% 범위에서 자동 조정한다.
+• MVP 참여 대상은 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주이며, 에이블리 기존 신규 광고주·무상 광고비 판정과 동일한 내부 광고 집행 이력 기준을 사용한다.
+• 최근 90일 주문 30건 이상, 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 기준은 신규 판정과 별도로 모두 충족해야 한다.
 • 카테고리 평균 주문금액 40,000원과 거래 수수료율 7%는 파일럿 수익 가정으로 모니터링한다.
 • 카테고리 평균 주문금액 또는 예상 거래 수수료 기여가 수익 가드 기준에 미달하면 상품가 구간별 전환 단가를 조정하거나 참여를 제한한다.
 • 예상 eCPM이 oCPM 바닥가의 95% 미만이면 우선순위를 낮추고 80% 미만이면 oCPM 캠페인으로 대체한다.
 • 셀러당 일일 노출 한도는 파일럿에서 지면 일일 노출의 5% 이하이다.
 • Phase 2 목표 CPA 입찰에서는 광고주 입찰 전환 단가가 eCPM의 직접 변수로 추가된다.
-• 데이터: - 참여 자격은 sellerId, 평가일, 주문수, 평점, 품절률, 배송품질, 평균주문금액, 예상수수료기여, 수익가드판정, 적격여부, 제한사유를 가진다.
+• 데이터: - 참여 자격은 sellerId, 평가일, 주문수, 평점, 품절률, 배송품질, 유상광고집행이력플래그, 평균주문금액, 예상수수료기여, 수익가드판정, 적격여부, 제한사유를 가진다.
+• 유상광고집행이력플래그는 해당 없음, 소액, 일반 중 하나로 저장한다.
 • 예측 결과는 campaignId, 지면Id, 예상전환율, 품질점수, 예상eCPM, 모델버전, 산정시각을 가진다.
 • 이상 탐지 기록은 탐지Id, 전환Id, 위험유형, 위험점수, 처리상태를 가진다.</t>
   </si>
@@ -393,7 +404,8 @@
 • 트리거: - 관리자가 참여 자격·한도·전환 검증·정산 메뉴를 선택한다.
 • 일일 가드레일 평가 또는 월간 청구서 생성 작업이 실행된다.
 • 광고주 이의 제기 또는 이상 탐지 경보가 접수된다.
-• 동작: - 관리자가 카테고리·지면·셀러 등급·상품 품질·예산·노출 한도를 설정한다.
+• 동작: - 관리자가 카테고리·지면·셀러 등급·상품 품질·예산·노출 한도와 졸업 셀러의 성과형 월 집행 상한을 설정한다.
+• 관리자가 최근 유상 광고 집행 이력, 품질 게이트, 누적 유효 전환 수를 확인해 신규·졸업 대기·졸업 상태를 검토한다.
 • 관리자가 잠정 전환의 주문·마지막 유효 클릭·전환 로그와 이상 탐지 결과를 검토해 승인·무효·보류 처리한다.
 • 플랫폼이 확정 전환 비용을 월간 청구서에 반영하고 환불·이의 조정액을 다음 달 청구서 또는 광고 크레딧으로 반영한다.
 • 플랫폼이 공짜 소진율과 별도로 카테고리 평균 주문금액 및 거래 수수료 기여를 수익 가드 지표로 모니터링한다.
@@ -405,7 +417,8 @@
 • 청구서 발행 후 이의가 접수되면 원 청구 내역을 보존하고 조정 건을 별도 생성한다.
 • 정산 연동 실패 시 청구서 상태를 발행 보류로 두고 재처리한다.
 • 가드레일 산출 데이터가 누락되면 자동 확대를 막고 운영자 검토로 전환한다.
-• 표시: - 콘솔은 참여 자격, 전환 검증 대기열, 정산·이의, 가드레일 모니터링을 분리해 표시한다.
+• 표시: - 콘솔은 신규 광고주 판정, 졸업 대기·졸업 상태, 참여 자격, 전환 검증 대기열, 정산·이의, 가드레일 모니터링을 분리해 표시한다.
+• 콘솔은 졸업 대상의 누적 유효 전환 수, oCPM 전환 안내 상태와 성과형 월 집행 상한을 표시한다.
 • 가드레일 위반은 영향 범위, 기준값, 현재값, 적용 조치를 표시한다.
 • 가드레일 화면은 공짜 소진율과 함께 카테고리 평균 주문금액·거래 수수료 기여를 표시한다.
 • 권한 &amp; 접근: - 플랫폼 관리자는 정책·한도 설정을 변경할 수 있다.
@@ -413,12 +426,12 @@
 • 광고 운영자는 담당 범위에서 자격·전환 검토를 수행할 수 있다.
 • 비즈니스 규칙: - 내부 전환은 D+7, 외부 전환은 D+14에 확정한다.
 • 전환 귀속은 기여 윈도우 안의 마지막 유효 클릭 1건만 인정하고 view-through 기여는 MVP에서 과금하지 않는다.
-• 청구서는 매월 1일~말일 확정분을 기준으로 다음 달 5일 발행하며 광고주는 발행 후 7일 이내 이의를 제기할 수 있다.
+• 누적 유효 전환 50건은 성과 검증 완료·oCPM 전환 안내 기준이며, 졸업 후 성과형 월 집행 상한을 적용한다.
 • 공짜 소진율이 20%를 초과하면 신규 성과형 캠페인 유입을 중단하고 기존 노출 한도를 축소한다.
-• 카테고리 평균 주문금액 또는 거래 수수료 기여가 수익 가드 기준에 미달하면 해당 카테고리의 단가 조정 또는 신규 참여 제한을 검토한다.
+• 신규 광고주 한정과 졸업 후 성과형 월 집행 상한은 eCPM 동일 경매·oCPM 바닥가 가드레일·지면 매출 유지율과 함께 기존 oCPM 매출 잠식을 막는 1차 장치이다.
 • CPD는 성과형 상품으로 자동 전환하지 않는다.
 • 데이터: - 정산 내역은 settlementId, campaignId, billingMonth, 확정전환수, 청구금액, 조정금액, 상태, 청구서Id를 가진다.
-• 가드레일 결과는 평가일, 카테고리, 지면, 공짜소진율, 매출유지율, 예측오차, 평균주문금액, 거래수수료기여, 수익가드판정, 조치상태를 가진다.
+• 가드레일 결과는 평가일, 카테고리, 지면, 신규광고주비중, 졸업셀러성과형집행액, 공짜소진율, 매출유지율, 예측오차, 평균주문금액, 거래수수료기여, 수익가드판정, 조치상태를 가진다.
 • 감사 로그는 actorId, 역할, 대상유형, 대상Id, 이전값, 변경값, 변경시각을 가진다.</t>
   </si>
   <si>
@@ -432,7 +445,7 @@
 1. ○ Given 파일럿 출시를 준비할 때, When 대상 카테고리·지면·셀러 수·기간과 사전 핵심 지표 임계값을 등록하면, Then 승인 전에는 집행을 시작할 수 없다.
 2. ○ Given 파일럿 평가 기간이 종료되었을 때, When 성장·수익성·건전성 지표를 산출하면, Then 확대·유지·축소·중단 중 하나의 결정을 기록한다.
 3. ○ Given 공짜 소진율이 20%를 초과하거나 지면 매출 유지율이 90% 미만으로 지속될 때, When 축소·중단 규칙이 평가되면, Then 신규 성과형 캠페인 유입을 중단하거나 기존 노출 한도를 축소한다.
-4. ○ Given Phase 2 후보를 검토할 때, When 외부 미입점 광고주·CPA 상한 보장·전환 건수 보장 항목을 등록하면, Then MVP 범위와 분리해 보류 상태로 관리한다.</t>
+4. ○ Given Phase 2에서 소액 기존 중소 셀러 확대를 검토할 때, When 운영 데이터와 머신러닝 학습 안정성을 평가하면, Then 졸업 기준 상향과 eCPM 경매·집행 상한 방어안을 MVP와 분리해 기록한다.</t>
   </si>
   <si>
     <t>중간</t>
@@ -441,7 +454,7 @@
     <t>6.1 파일럿 게이트와 단계적 확대 관리</t>
   </si>
   <si>
-    <t xml:space="preserve">파일럿 대상·기간·핵심 지표 게이트를 등록하고 결과에 따라 확대·유지·축소·중단을 결정하는 기능이다. 외부 미입점 광고주, 목표 CPA 입찰, CPA 상한 및 전환 건수 보장은 Phase 2 후보로 별도 관리한다.
+    <t xml:space="preserve">파일럿 대상·기간·핵심 지표 게이트를 등록하고 결과에 따라 확대·유지·축소·중단을 결정하는 기능이다. MVP는 유상 광고 집행 이력이 없는 신규 광고주로 대상을 한정하고, 누적 유효 전환 50건의 졸업 트리거와 성과형 월 집행 상한으로 기존 oCPM 매출 잠식을 방어한다. 외부 미입점 광고주, 목표 CPA 입찰, CPA 상한 및 전환 건수 보장은 Phase 2 후보로 별도 관리한다.
 [기능의 근거] 제한된 파일럿에서 수익성과 건전성을 검증한 뒤 안전하게 대상 카테고리와 셀러를 확대해야 한다.
 [성공 기준] 신규 성과형 광고주 수 300명과 성과형 광고 매출 비중 5% 이상을 달성한다.
 [개발 준비 슬롯]
@@ -451,8 +464,9 @@
 • 일일 모니터링 또는 파일럿 종료 평가가 실행된다.
 • 확대·축소·중단 임계값을 충족한다.
 • 동작: - 관리자가 패션·뷰티, 전환이 활발한 기존 지면, 초기 대상 셀러를 등록한다.
-• 플랫폼이 성장·수익성·건전성 지표를 파일럿·확대·축소 기준과 비교한다.
+• 플랫폼이 성장·수익성·건전성 지표와 신규 한정·집행 상한의 매출 잠식 방어 효과를 파일럿·확대·축소 기준과 비교한다.
 • 플랫폼이 확대·유지·축소·중단 결정을 기록하고 대상·노출 한도에 반영한다.
+• Phase 2에서 소액 기존 중소 셀러 확대를 검토할 때 플랫폼은 내부 머신러닝 학습 안정성과 운영 데이터를 바탕으로 졸업 기준 상향안을 평가한다.
 • FE는 게이트 설정과 결과 화면을 만들고 BE는 승인·결정 상태를 처리하며 Data·ML은 지표 산출을 제공하고 정산은 총 기여 산정 데이터를 제공한다.
 • 결과: - 파일럿 계획, 승인, 지표 스냅샷, 의사결정 및 후속 조치를 저장한다.
 • 확대 결정 시 대상 카테고리·지면·셀러 범위를 늘리고 축소·중단 시 한도를 줄인다.
@@ -467,10 +481,12 @@
 • 광고 운영자와 데이터·분석 담당자는 결과를 조회하고 근거를 제출할 수 있다.
 • 비즈니스 규칙: - 파일럿은 패션·뷰티와 기존 활성 상품광고 지면을 우선 대상으로 한다.
 • 초기 파일럿은 카테고리별 20~30개, 총 100개 레퍼런스 셀러를 목표로 한다.
+• MVP 참여 대상은 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주이며, 기존 품질 게이트를 유지한다.
 • 확대 게이트는 신규 광고주 500명 이상, 전환 발생률 40% 이상, 재집행률 35% 이상, 성과형 광고 매출 비중 10% 이상이다.
+• Phase 2에서 소액 기존 중소 셀러로 확대할 때는 졸업 기준 50건 상향을 검토하고, eCPM 동일 경매와 성과형 월 집행 상한으로 기존 oCPM 매출 잠식을 방어한다.
 • 외부 미입점 광고주, 목표 CPA 입찰, CPA 상한 보장, 전환 건수 보장은 Phase 2 후보이다.
 • 데이터: - 파일럿 계획은 pilotId, 대상카테고리, 대상지면, 대상셀러수, 시작·종료일, 승인상태, 게이트버전을 가진다.
-• 지표 스냅샷은 pilotId, 기준일, 신규광고주수, 전환발생률, 재집행률, 매출비중, 매출유지율, 공짜소진율, 예측오차, 결정값을 가진다.
+• 지표 스냅샷은 pilotId, 기준일, 신규광고주수, 전환발생률, 재집행률, 매출비중, 매출유지율, 공짜소진율, 예측오차, 졸업셀러수, oCPM전환안내율, 결정값을 가진다.
 • Phase 2 후보는 후보Id, 이름, 범위, 보류사유, 재검토조건, 상태를 가진다.</t>
   </si>
   <si>
@@ -500,14 +516,14 @@
 MVP 권장안: - MVP는 카테고리별 기준단가 자동 조정 방식을 적용한다.
 - 패션·뷰티의 구매 전환 기준단가는 4,000원을 파일럿 가정으로 사용한다.
 - 쿠폰 사용 전환 기준단가는 1,500원을 파일럿 가정으로 사용한다.
-- 앱 설치 전환 기준단가는 2,500원을 파일럿 가정으로 사용한다.
+- 앱 설치 전환은 MVP 기본 전환 유형에서 제외하고 해당 캠페인에 한해 별도 승인 후 적용하거나 Phase 2에서 도입한다.
 - 전환 단가는 지면·상품·셀러의 예상 전환율과 품질 점수에 따라 기준단가의 80~120% 범위에서 조정한다.
 - 광고주에게는 적용 단가, 조정 요인, 예상 전환 수와 예상 비용을 캠페인 생성 전에 고지한다.
-단가 조정: - 플랫폼은 카테고리·지면별 전환율과 마진을 매주 검토한다.
+저가 상품 수익 가드: Q. 카테고리 평균 주문금액이 파일럿 기준 40,000원보다 낮을 때 어떤 수익 가드를 적용할까요?
+단가 조정: - 플랫폼은 카테고리·지면별 전환율, 마진, 평균 주문금액과 거래 수수료 기여를 매주 검토한다.
 - 카테고리·지면의 실제 eCPM이 기준 대비 10% 이상 낮게 7일 지속되면 다음 주기 기준단가를 상향 조정한다.
 - 카테고리·지면의 실제 eCPM이 기준 대비 20% 이상 높고 재집행률이 35% 이상이면 다음 주기 기준단가 인하를 검토한다.
-- 이미 시작된 캠페인의 단가는 해당 일일 예산 주기 동안 유지하고, 변경은 다음 일일 예산 주기부터 적용한다.
-순수 성과형 상품광고의 전환 단가를 산정·제시·조정하는 기준이다. 모든 금액과 임계값은 파일럿 가정이며, 카테고리·지면별 과거 데이터 검증 뒤 확정한다.</t>
+- 이미 시작된 캠페인의 단가는 해당 일일 예산 주기 동안 유지하고, 변경은 다음 일일 예산 주기부터 적용한다.</t>
   </si>
   <si>
     <t>PL-ZJSKLL</t>
@@ -535,16 +551,18 @@
 - 외부 전환은 광고주 포스트백 또는 전환 API 수신 후 잠정 집계하고 D+14에 유효 여부를 확정한다.
 - 확정 전환 비용은 매일 누적 표시하고, 광고주 청구서는 매월 1일~말일 확정분을 기준으로 다음 달 5일 발행한다.
 - 광고주는 청구서 발행 후 7일 이내에 이의를 제기할 수 있다.
-유효 전환 기준: - 구매 전환은 광고 기여 윈도우 안에 발생한 결제 완료 주문만 유효 전환으로 인정한다.
+유효 전환 기준: - MVP의 유효 전환 유형은 구매와 쿠폰 사용이며 앱 설치 전환은 해당 캠페인에 한해 별도 승인 후 적용하거나 Phase 2에서 도입한다.
+- 구매 전환은 광고 기여 윈도우 안에 발생한 결제 완료 주문만 유효 전환으로 인정한다.
 - 쿠폰 사용 전환은 광고 기여 윈도우 안에 발생한 유효 쿠폰 사용만 유효 전환으로 인정한다.
-- 동일 주문·동일 쿠폰 사용·동일 설치 이벤트는 한 번만 과금한다.
+- 전환 귀속은 기여 윈도우 안의 마지막 유효 클릭 1건만 인정하며, 한 전환에 복수 광고 클릭이 있으면 가장 늦은 유효 클릭의 캠페인에만 귀속한다.
+- 노출만 발생한 view-through 기여는 MVP의 과금·정산 대상에서 제외한다.
+- 동일 주문·동일 쿠폰 사용 이벤트는 한 번만 과금한다.
 - 취소·환불·부정 거래·셀프 구매·정책 위반 전환은 과금 대상에서 제외한다.
 - 광고 기여 윈도우 일수는 캠페인 유형별로 설정하고 파일럿 기본값은 클릭 후 7일로 둔다.
 분쟁·환불 조정: - 이상 패턴이 탐지된 전환 비용은 검증 완료 전까지 정산 보류 상태로 표시한다.
-- 광고주 이의 제기는 주문·클릭·전환 로그와 어뷰징 판정 결과를 기준으로 검토한다.
+- 광고주 이의 제기는 주문·마지막 유효 클릭·전환 로그와 어뷰징 판정 결과를 기준으로 검토한다.
 - 확정 후 취소·환불이 발생한 전환 비용은 다음 달 청구서에서 차감한다.
-- 이미 납부한 비용의 조정액은 다음 달 광고 크레딧으로 우선 반영한다.
-유효 전환의 검증, 과금 확정, 정산과 분쟁 조정을 일관되게 처리하는 정책이다.</t>
+- 이미 납부한 비용의 조정액은 다음 달 광고 크레딧으로 우선 반영한다.</t>
   </si>
   <si>
     <t>PL-PVAXPM</t>
@@ -554,18 +572,22 @@
   </si>
   <si>
     <t xml:space="preserve">파일럿 대상: - 파일럿은 패션·뷰티 카테고리와 전환이 활발한 기존 상품광고 지면을 우선 대상으로 한다.
-- 초기 초대 대상은 최근 90일 주문 30건 이상, 상품 평점 4.2점 이상, 품절률 5% 미만인 입점 셀러로 선정한다.
+- MVP 대상은 최근 N개월 유상 광고 집행 이력이 0원인 입점 신규 광고주이며, 에이블리 기존 신규 광고주·무상 광고비 판정과 같은 내부 광고 집행 이력으로 판단한다.
+- 별도 매출·거래액 증빙 서류는 요구하지 않는다.
+- 초기 초대 대상은 최근 90일 주문 30건 이상, 상품 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 기준을 충족한 셀러로 선정한다.
 - 배송 지연·취소율과 정책 위반 이력이 내부 기준을 초과한 셀러는 파일럿 대상에서 제외한다.
 - 카테고리별 20~30개, 총 100개 레퍼런스 셀러를 1차 모집 목표로 둔다.
 세일즈 메시지: - 초대 메시지는 ‘성과 없으면 0원, 구매·쿠폰 사용 전환 발생분만 과금’을 핵심 문구로 사용한다.
 - 초대 메시지는 권장 상품, 예상 전환 수, 예상 비용 범위와 기존 상품광고 지면 정보를 함께 제공한다.
+- 누적 유효 전환 50건에 근접한 셀러에게는 성과 검증 완료 예정과 oCPM 유상 광고 전환 안내를 제공한다.
 - BD 담당자는 첫 캠페인 성과가 확인된 셀러의 전환율·광고 기여 매출 사례를 익명화해 같은 카테고리 셀러에게 제시한다.
-온보딩 흐름: - 셀러는 초대 메시지에서 셀러센터의 성과형 상품광고 소개 화면으로 진입한다.
+온보딩·졸업 흐름: - 셀러는 초대 메시지에서 셀러센터의 성과형 상품광고 소개 화면으로 진입한다.
 - 셀러는 대상 상품을 선택하고 권장 전환 단가·일일 예산·예상 비용을 확인한다.
 - 셀러는 전환 과금·검증·환불 조정 기준에 동의한 후 캠페인을 시작한다.
-- BD 또는 셀러센터는 시작 후 7일에 성과 리포트와 예산·상품 조정 제안을 제공한다.
-- 성과 기준을 충족한 셀러에는 30일 내 재집행 제안을 제공한다.
-중소·신규 셀러를 파일럿에 모집하고 첫 캠페인과 재집행으로 연결하는 BD 운영 기준이다.</t>
+- 셀러 상태는 신규-성과형에서 누적 유효 전환 50건 근접 시 졸업 대기로 전이한다.
+- 셀러 상태는 누적 유효 전환 50건 달성 시 졸업으로 전이하고 oCPM 유상 광고 전환을 안내한다.
+- 졸업 셀러는 성과형 월 집행 상한 안에서 성과형 캠페인을 계속 사용할 수 있다.
+- BD 또는 셀러센터는 시작 후 7일에 성과 리포트와 예산·상품 조정 제안을 제공한다.</t>
   </si>
   <si>
     <t>PL-BDBECW</t>
@@ -575,17 +597,19 @@
   </si>
   <si>
     <t xml:space="preserve">[공통 정의]
-용어 정의: - 유효 전환은 기여 윈도우 안에 발생하고 중복·취소·환불·부정 거래·정책 위반 검증을 통과해 과금 가능한 전환이다.
+용어 정의: - 유효 전환은 기여 윈도우 안에 발생하고 마지막 유효 클릭 기준 귀속, 중복·취소·환불·부정 거래·정책 위반 검증을 통과해 과금 가능한 구매 또는 쿠폰 사용 전환이다.
+- 마지막 유효 클릭은 전환 발생 전 기여 윈도우 안에 있는 광고 클릭 중 가장 늦은 유효 클릭이며, 한 전환은 해당 클릭 1건에만 귀속한다.
+- view-through 기여는 광고 노출만으로 전환을 귀속하는 방식이며 MVP의 측정·과금·정산에서 제외한다.
 - 공짜 소진율은 성과형 캠페인에 배정된 노출 중 유효 전환 비용이 발생하지 않은 노출의 비율이다.
 - eCPM은 예상 전환율×전환 단가×1,000으로 계산하는 경매 비교값이다.
 - 기여 윈도우는 광고 클릭 후 전환을 광고 기여로 인정하는 기간이며 파일럿 기본값은 7일이다.
 - 증분성은 자연전환과 기존 oCPM 베이스라인을 제외한 신규 셀러의 광고 기여 증분 GMV와 수수료 기여를 뜻한다.
-데이터 모델: - 캠페인은 campaignId, sellerId, 상품Id, 전환유형, 상태, 기간, 예산, 적용전환단가, 누적비용, 잔여예산을 저장한다.
-- 전환 이벤트는 conversionId, idempotencyKey, campaignId, 원이벤트Id, 발생·수신시각, 기여클릭Id, 검증상태, 무효사유, 적용단가를 저장한다.
+데이터 모델: - 캠페인은 campaignId, sellerId, 상품Id, 전환유형, 상태, 기간, 예산, 적용전환단가, 누적비용, 잔여예산, 상품가구간, 수익가드판정을 저장한다.
+- 전환 이벤트는 conversionId, idempotencyKey, campaignId, 원이벤트Id, 발생·수신시각, 마지막유효클릭Id, 검증상태, 무효사유, 적용단가를 저장한다.
 - 정산 내역은 settlementId, campaignId, 청구월, 확정전환수, 청구금액, 조정금액, 상태, 청구서Id를 저장한다.
-- 셀러 참여 자격은 sellerId, 평가일, 주문수, 평점, 품절률, 배송품질, 적격여부, 제한사유를 저장한다.
+- 셀러 참여 자격은 sellerId, 평가일, 주문수, 평점, 품절률, 배송품질, 평균주문금액, 예상수수료기여, 수익가드판정, 적격여부, 제한사유를 저장한다.
 상태 머신: - 캠페인은 초안에서 심사로 전이하고 심사 승인 후 집행중으로 전이한다.
-- 캠페인은 예산·품질·가드레일 위반 시 제한으로 전이하며, 운영자 또는 정책 판단으로 중단으로 전이한다.
+- 캠페인은 예산·품질·수익 가드·가드레일 위반 시 제한으로 전이하며, 운영자 또는 정책 판단으로 중단으로 전이한다.
 - 전환은 잠정 집계에서 내부 전환 D+7 또는 외부 전환 D+14 검증을 거쳐 확정으로 전이한다.
 - 전환은 검증 실패 시 무효로 전이하고 확정 후 취소·환불 시 환불 차감으로 전이한다.
 [지표·연동]
@@ -593,22 +617,46 @@
 - 유효 전환율은 유효 전환 수÷성과형 광고 노출 수×100으로 계산한다.
 - 공짜 소진율은 유효 전환 비용이 발생하지 않은 성과형 광고 노출 수÷성과형 광고 노출 수×100으로 계산한다.
 - 지면 매출 유지율은 성과형과 oCPM을 합산한 실제 지면 매출÷기존 oCPM 베이스라인 지면 매출×100으로 계산한다.
+- 평균 주문금액은 유효 구매 전환의 주문금액 합계÷유효 구매 전환 수로 계산한다.
+- 거래 수수료 기여는 광고 기여 증분 GMV×거래 수수료율로 계산하며 파일럿 수수료율은 7%로 둔다.
 - 총 기여 기준 손익분기 유효 전환율은 기존 oCPM÷((전환단가×(1-공짜소진율)+평균주문금액×거래수수료율)×1,000)으로 계산한다.
-API·연동 명세: - 외부 전환 API·포스트백 요청은 idempotencyKey, conversionId, campaignId, eventType, occurredAt, orderOrEventId, value, currency를 포함한다.
-- 외부 전환 API·포스트백 응답은 accepted, conversionId, processingStatus, receivedAt, errorCode를 포함한다.
-- idempotencyKey는 전환 소스와 원이벤트 식별자를 조합한 유일값이며 동일 키 요청은 최초 처리 결과를 반환한다.
-- 내부 결제·주문·쿠폰 로그는 결제 완료, 취소, 환불, 쿠폰 사용 이벤트와 campaignId 또는 기여클릭Id 연결값을 전환 수집 서비스에 전달한다.
+API·연동 명세: Q. 외부 전환 API·포스트백의 재전송 횟수와 지수 백오프 상한을 어떤 파일럿 기준으로 적용할까요?
 [화면·품질]
 화면 명세: - 셀러 캠페인 생성 화면은 상품 선택, 전환 유형, 예산·기간 입력, 적용 단가·예상 전환 수·예상 비용 검토, 약관 동의 순서로 제공한다.
 - 셀러 성과 대시보드는 노출, 클릭, 잠정·확정 전환, 전환율, 전환당 비용, 누적 비용, 잔여 예산, 과금 근거, 제한 알림을 제공한다.
-- 관리자 콘솔은 참여 자격, 전환 검증 대기열, 정산·이의 조정, 공짜 소진율·매출 유지율·예측 오차 가드레일을 제공한다.
+- 관리자 콘솔은 참여 자격, 전환 검증 대기열, 정산·이의 조정, 공짜 소진율·매출 유지율·예측 오차·평균 주문금액·거래 수수료 기여 가드레일을 제공한다.
 - 관리자 콘솔은 설정·검증·정산·가드레일 변경의 감사 이력을 제공한다.
-비기능 요구사항: - 전환 집계는 원이벤트 수신 시 잠정 집계하고 검증 결과가 바뀌면 상태와 비용을 재계산한다.
-- 내부 전환은 D+7, 외부 전환은 D+14 확정 기준을 적용하며 지연 수신 이벤트는 원 발생 시각과 수신 시각을 함께 보관한다.
-- 정산 금액은 원화 정수 금액으로 저장하고 확정 전환·조정 내역과 청구서 간 추적 가능한 대사 기록을 보관한다.
-- 개인정보와 주문 원본 식별자는 역할 기반 접근 통제를 적용하고 광고주 화면에는 비식별 근거만 제공한다.
-- 캠페인·전환·정산·가드레일의 생성·변경·판정·API 수신은 행위자와 시각을 포함한 감사 로그로 남긴다.
-순수 성과형 상품광고의 공통 용어, 데이터 구조, 상태 전이, 연동, 화면 및 비기능 기준을 정의한다. 모든 수치와 기준은 파일럿 가정이며, 기존 전환 단가·경매·정산·GTM 정책을 우선 적용한다.</t>
+비기능 요구사항: Q. 외부 전환 수신과 대시보드 반영 SLA를 어떤 파일럿 기준으로 적용할까요?</t>
+  </si>
+  <si>
+    <t>PL-ZWIDEK</t>
+  </si>
+  <si>
+    <t>신규 광고주 참여 및 졸업 정책</t>
+  </si>
+  <si>
+    <t xml:space="preserve">신규 광고주 정의: - 신규 광고주는 최근 N개월 유상 광고 집행 이력이 0원인 입점 셀러이다.
+- 유상 광고 집행 이력은 에이블리 기존 신규 광고주·무상 광고비 판정과 동일한 내부 광고 집행 이력 기준으로 판단한다.
+- 신규 광고주 판정에는 별도 매출·거래액 증빙 서류를 요구하지 않는다.
+- 유상 광고 집행 이력 플래그는 해당 없음, 소액, 일반 중 하나로 저장한다.
+참여 품질 게이트: - 신규 광고주는 최근 90일 주문 30건 이상을 충족한 경우에만 MVP 성과형 상품광고에 참여할 수 있다.
+- 신규 광고주는 상품 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 내부 기준을 모두 충족한 경우에만 MVP 성과형 상품광고에 참여할 수 있다.
+- 품질 게이트 미충족, 수익 가드 미충족 또는 정책 위반 셀러는 신규 판정과 관계없이 참여를 제한한다.
+성과 검증 및 졸업: - 캠페인과 셀러 상태는 신규-성과형, 졸업 대기, 졸업 순서로 전이한다.
+- 누적 유효 전환 수가 50건에 도달하면 성과 검증 완료로 기록하고 졸업 상태로 전이한다.
+- 졸업 상태의 셀러에게는 oCPM 유상 광고 전환을 안내한다.
+- 졸업 후에도 셀러는 성과형 상품광고를 사용할 수 있다.
+- 누적 유효 전환 50건은 공개 벤치마크와 실무 권장 범위를 참고한 보수적 파일럿 가정이며, 내부 머신러닝 최소 학습 전환 기준과 운영 데이터로 보정한다.
+성과형 월 집행 상한: - 졸업 셀러는 기존 oCPM 매출 잠식을 제한하기 위해 성과형 월 집행 상한을 적용한다.
+- 성과형 월 집행 상한은 eCPM 동일 경매와 oCPM 바닥가 가드레일을 대체하지 않고 함께 적용한다.
+Phase 2 확대: - Phase 2에서 소액 기존 중소 셀러로의 확대를 검토한다.
+- Phase 2 확대 시 내부 머신러닝 학습 안정성과 운영 데이터를 기준으로 졸업 기준을 50건보다 상향하는 방안을 검토한다.
+- Phase 2에서도 eCPM 동일 경매와 성과형 월 집행 상한으로 기존 oCPM 매출 잠식을 방어한다.
+기존 정책 우선순위: - 전환 단가 책정은 전환 단가 책정 정책을 우선 적용한다.
+- 노출 경쟁·eCPM·oCPM 바닥가 가드레일은 상품광고 경매 및 노출 배분 정책을 우선 적용한다.
+- 유효 전환 판정과 정산은 전환 확정 및 정산 정책을 우선 적용한다.
+- 초대·온보딩 운영은 성과형 상품광고 GTM 및 온보딩 정책을 우선 적용한다.
+MVP 성과형 상품광고의 신규 광고주 판정, 성과 검증 후 oCPM 전환 안내 및 집행 상한을 정한다. 전환 단가·경매·전환 확정·정산·GTM 세부 규칙은 기존 정책을 우선 적용한다.</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1400,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" ht="653.4000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" ht="732.6" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -1364,7 +1412,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" ht="198.00000000000003" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" ht="257.40000000000003" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1735,7 +1783,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D7"/>
+  <dimension ref="B2:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1810,6 +1858,17 @@
         <v>92</v>
       </c>
     </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/ably/assets/ably-performance-ad-prd.xlsx
+++ b/ably/assets/ably-performance-ad-prd.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="100">
   <si>
     <t>에이블리 입점 중소·신규 셀러를 위한 순수 성과형 상품광고</t>
   </si>
@@ -41,71 +41,73 @@
     <t>제품 목표</t>
   </si>
   <si>
-    <t>기존 oCPM 상품광고에 전환 발생 시에만 과금하는 순수 성과형(Pay-for-Performance) 레이어를 추가해 광고주의 선투자와 성과 미달 위험을 제거한다. 초기 광고비 부담이 큰 중소·신규 셀러가 소액으로 상품광고를 시작하고 구매·쿠폰 사용·앱 설치 등 검증 가능한 전환이 발생한 경우에만 비용을 지불하도록 한다. oCPM으로 유입되지 않던 신규 셀러를 활성화해 광고비뿐 아니라 광고 기여 증분 GMV의 거래 수수료까지 창출함으로써 롱테일 광고주 풀, 신규 광고주 수, 재집행률, 광고주 LTV 및 에이블리 총 기여를 확대한다. 기존 oCPM·CPD 매출의 수익성은 eCPM 경매와 노출 가드레일로 방어한다.</t>
+    <t>홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯에 신규 광고주 한정 전환 성과형 과금 옵션을 추가한다. 유효 전환이 확정된 경우에만 비용을 청구해 신규 셀러의 선투자 위험을 없애고, 추천 AI의 예상 전환율로 기존 oCPM과 같은 슬롯에서 경쟁시켜 지면 수익을 방어한다. 오가닉 추천과 겹치는 발견 지면의 특성은 holdout 대조군으로 증분성을 검증해, 광고비와 순증분 거래 수수료를 포함한 에이블리 총 기여를 늘린다.</t>
   </si>
   <si>
     <t>배경</t>
   </si>
   <si>
-    <t>에이블리는 MAU 1,067만 명과 구매·결제 데이터를 보유한 버티컬 커머스 플랫폼이다. 현재 상품광고 지면은 주로 oCPM으로 운영되며, 투데이 추천상품, 투데이·검색결과의 유사 상품 추천, 상품상세 연관추천, 검색 기반 지면처럼 전환이 활발한 인피드 지면이 이미 존재한다. MVP는 배너·구좌형 디스플레이 광고나 신규 지면을 만드는 일이 아니라, 기존 활성 상품광고 지면에 전환 시에만 과금하는 레이어를 적용하는 방식이다. 입점 셀러의 광고 기여 구매는 광고비와 함께 플랫폼 3%·결제 3.96%를 합산한 약 7%의 거래 수수료를 추가로 만들 수 있다. 대형 브랜드의 CPD 상품은 유지해 매출 잠식을 방지하고, 거래 수수료가 발생하지 않는 외부 미입점 광고주·CPA 상한 보장·전환 건수 보장은 Phase 2로 둔다.</t>
+    <t>에이블리는 개인화 추천·발견 커머스이며, 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’은 최대 인벤토리이자 핵심 자산이다. 현행 DA 구좌, 셀러 배너, oCPM 상품광고, 메타 연계 광고는 노출 또는 기간 기반으로 운영되고, 이 추천 피드의 기존 sponsored 슬롯도 oCPM 추정 과금이다. 따라서 ‘전환됐을 때만 내는 순수 성과형’은 플랫폼에 없는 화이트스페이스이며, 신규 지면 개발이 아니라 기존 sponsored 슬롯의 과금 옵션을 추가하는 방식으로 MVP를 만든다.</t>
   </si>
   <si>
     <t>사용자 문제</t>
   </si>
   <si>
-    <t>대형 브랜드는 높은 예산으로 CPD 광고를 집행할 수 있지만, 중소 셀러와 신규 광고주는 수백만~천만 원대의 선불 비용과 성과 불확실성을 감당하기 어렵다. 광고주는 상품광고 노출·클릭이 실제 구매로 이어졌는지 확인하기 어렵고, 성과가 없을 때 광고비를 전액 잃을 수 있다는 두려움 때문에 광고를 시작하거나 재집행하지 않는다. 플랫폼은 전환 가능성이 낮은 캠페인에 노출을 제공하면 무료 인벤토리 소진과 기존 oCPM 매출 기회비용을 부담할 수 있다.</t>
+    <t>중소·신규 셀러는 노출·기간 기반 광고의 선불 비용과 성과 불확실성 때문에 광고 시작과 재집행을 망설인다. 에이블리의 핵심 지면은 검색보다 개인화 추천·발견이므로, 검색형 성과광고 방식을 그대로 적용하면 저의도 탐색 상황에서 무료 노출 소진과 기존 oCPM 매출 잠식 위험이 커진다. 또한 발견 지면의 광고 상품은 오가닉 추천과 함께 노출되므로 광고가 없어도 발생했을 전환까지 성과로 인정하면 광고 기여와 거래 수수료를 과대평가한다.</t>
   </si>
   <si>
     <t>해결 방안</t>
   </si>
   <si>
-    <t>기존 전환 중심 상품광고 지면에 순수 성과형 과금 방식을 적용한다. 광고주는 예산과 목표 상품을 설정하고, 노출·클릭이 아니라 기여가 인정된 구매·쿠폰 사용·앱 설치가 발생한 경우에만 전환 단가를 지불하며, 전환이 없으면 비용을 청구하지 않는다. 성과형 캠페인은 예상 전환율×전환 단가로 eCPM 환산값을 계산해 oCPM 캠페인과 같은 경매 기준으로 경쟁시키고, 예상 eCPM이 지면 기준을 밑돌면 우선순위를 낮추거나 oCPM 캠페인으로 대체한다. 내부 결제·쿠폰 로그와 외부 전환 API·포스트백을 활용해 전환을 측정하고, 기여 윈도우·중복 제거·자연전환 구분·환불 조정을 적용한다.</t>
+    <t>홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 광고주에게만 순수 성과형 과금 옵션을 제공한다. 추천 상품 카드와 같은 네이티브 UI 및 ‘광고’ 라벨을 유지하고, 추천 N개당 광고 1개 밀도 캡 안에서 노출한다. 신규 성과형은 추천 AI 예상 전환율×플랫폼 제시 전환 단가로 eCPM을 계산해 기존 oCPM과 동일 경매에서 경쟁하며, eCPM·추천 적합도·품질의 최소 기준을 넘지 못하면 노출하지 않는다. last-click 7일은 과금 귀속에만 사용하고, holdout 대조군의 노출군·미노출 유사 이용자 전환 차이로 산정한 순증분 전환은 수익 검증과 정산 보정에 사용한다.</t>
   </si>
   <si>
     <t>차별점</t>
   </si>
   <si>
-    <t>토스의 전환·주문 시 과금형 상품, 당근의 지역·관심사 기반 성과형 광고, 네이버의 CPC·성과형 광고를 벤치마크하되, 에이블리는 구매·결제 데이터, 커머스 내부 전환 로그, AI 추천 상품광고 지면과 입점 셀러 거래 수수료를 함께 활용할 수 있다. 핵심 가치는 oCPM으로는 유입되지 않던 신규 셀러를 성과 보장형 진입 경험으로 활성화하고, 이들이 만드는 광고 기여 증분 GMV와 그에 따른 약 7% 거래 수수료를 순증분으로 창출하는 데 있다. 해당 수수료는 기존 oCPM 베이스라인에 포함되지 않은 기여로 평가한다. 전환 단가와 예상 전환율을 결합한 eCPM 경매로 광고주의 금전 리스크는 0원으로 낮추되 플랫폼의 인벤토리 수익을 방어한다. 거래 수수료가 없는 외부 미입점 광고주는 순수 광고 수익성만으로 성립해야 하므로, 입점 셀러의 총 기여를 검증한 뒤 Phase 2에서 검토한다.</t>
+    <t>에이블리의 차별점은 두 가지다. 첫째, 추천 AI의 사용자·상품 맥락별 예상 전환율, 구매·결제 데이터, 메타 연계 전환 추적 역량이 저의도 발견 지면에서도 성과형을 성립시키는 조건이므로 검색 플레이북을 단순 복제할 수 없다. 둘째, 오가닉 추천과 겹치는 발견의 본질을 숨기지 않고 holdout 증분성으로 광고가 실제로 만든 순증분 전환만 측정·보정한다. 브랜드에는 발견 지면에서 브랜드를 모르는 신규 고객에게 도달하고 그 획득 성과에만 비용을 내는 상품으로 제안한다.</t>
   </si>
   <si>
     <t>타겟 사용자</t>
   </si>
   <si>
-    <t>1순위는 에이블리에 입점한 중소·신규 셀러다. 구체적으로 월 광고 예산이 수십만~수백만 원 수준이고 자체 마케팅 인력이나 광고 운영 경험이 제한적이며, 패션·뷰티 등 에이블리 내 상품 수요와 전환 가능성이 높은 카테고리의 상품을 판매하는 사업자다. 초기 초대 대상은 최근 90일 주문 30건 이상, 상품 평점 4.2점 이상, 품절률 5% 미만, 배송 지연·취소율이 내부 기준 이하인 셀러로 가정한다. 2순위는 매출과 재구매를 확대하려는 성장 단계 브랜드·셀러이며, 대형 브랜드는 기존 CPD 상품을 유지하는 별도 사용자군으로 관리하고 외부 미입점 광고주는 MVP 대상에서 제외한다.</t>
+    <t>1순위는 최근 N개월 유상 광고 집행 이력이 0원이고 기존 품질 게이트를 충족한 에이블리 입점 중소·신규 셀러다. 이들은 월 광고 예산이 수십만~수백만 원 수준이고 마케팅 인력·운영 경험이 제한적이지만, 패션·뷰티 등 홈 개인화 추천 피드에서 발견될 수 있는 상품을 판매한다. 2순위는 브랜드를 아직 모르는 신규 고객에게 도달해 신규 고객 획득을 늘리고 싶은 성장 단계 셀러이며, 대형 브랜드 CPD와 외부 미입점 광고주는 MVP 대상에서 제외한다.</t>
   </si>
   <si>
     <t>사용자 시나리오</t>
   </si>
   <si>
-    <t>1) 광고 운영자가 최근 90일 판매·재고·평점·배송 품질과 카테고리 전환율을 기준으로 파일럿 대상 셀러를 선정하고, 인앱 배너·셀러센터 알림·BD 아웃바운드로 ‘성과 없으면 0원, 구매·쿠폰 사용 전환 발생분만 과금’ 메시지를 안내한다. 2) 신규 셀러는 상품과 일일 예산을 선택하고, 권장 전환 단가·예상 전환 수·예상 비용을 확인한 뒤 성과형 상품광고 캠페인을 개설한다. 3) 기존 추천·검색·상품상세 인피드 지면에 광고가 노출되고 유효 전환이 발생한 경우에만 비용이 확정되며, 성과가 없는 노출은 과금되지 않는다. 4) 셀러는 대시보드에서 광고 기여 전환 수·전환율·전환당 비용·누적 비용·자연전환 대비 광고 기여전환을 확인하고 예산·상품을 조정한다. 5) 파일럿에서는 카테고리별 20~30개 레퍼런스 셀러를 우선 확보해 전환율·매출 상승 사례를 만들고, 주간 성과 리포트와 재집행 제안으로 확산한다.</t>
+    <t>1) 광고 운영자는 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 sponsored 슬롯과 추천 N개당 광고 1개 밀도 캡을 파일럿 범위로 등록한다. 2) 신규 셀러는 셀러센터에서 성과형 캠페인을 만들고 상품·예산·기간을 입력한 뒤, 추천 AI 예측에 기반한 플랫폼 제시 전환 단가와 예상 성과를 확인한다. 3) 적합도·품질·예상 eCPM 최소 기준을 통과한 캠페인만 기존 oCPM 캠페인과 같은 sponsored 슬롯 경매에 참여하며, 유효 전환 발생 시에만 과금된다. 4) 광고주와 운영자는 last-click 과금 전환과 holdout 기반 순증분 전환을 분리해 보고, 오가닉 추천 잠식과 신규 고객 획득을 함께 검증한다. 5) 누적 유효 전환 50건을 달성한 셀러는 oCPM 전환을 안내받고 성과형은 월 집행 상한 안에서 계속 이용한다.</t>
   </si>
   <si>
     <t>핵심 지표</t>
   </si>
   <si>
-    <t xml:space="preserve">MVP 수치 가정과 파일럿 게이트는 다음과 같다.
+    <t xml:space="preserve">모든 수치와 임계값은 홈 개인화 추천 피드 sponsored 슬롯 파일럿 가정이며 운영 데이터로 보정한다.
 구분  지표  파일럿 목표  확대 게이트  축소·중단 기준성장  신규 성과형 광고주 수  300명  500명 이상  200명 미만
-성장  첫 캠페인 전환 발생률(활성화율)  35% 이상  40% 이상  25% 미만
+성장  첫 캠페인 전환 발생률  35% 이상  40% 이상  25% 미만
 성장  30일 재집행률  30% 이상  35% 이상  20% 미만
-성장  성과형 광고 매출 비중  파일럿 지면 매출의 5% 이상  10% 이상  3% 미만
+성장  신규 고객 도달 수·획득 수  기준선 설정  증가 추세  기준선 하회 지속
 수익성  지면 매출 유지율  기존 oCPM 대비 95% 이상  100% 이상  90% 미만
+수익성  성과형 광고 매출 비중  파일럿 슬롯 매출의 5% 이상  10% 이상  3% 미만
+증분성  증분 전환율  holdout 기준 양수  통계적 신뢰도 충족  0 이하 또는 표본 미달 지속
+증분성  오가닉 추천 잠식률  파일럿 기준선 이하  기준선 유지  운영 목표 초과
 건전성  공짜 소진율  15% 이하  10% 이하  20% 초과
 건전성  전환 예측 오차  절대오차 20% 이하  15% 이하  30% 초과
-건전성  유효 전환율  0.15% 이상  0.18% 이상  0.12% 미만
-신규 한정과 성과형 월 집행 상한은 eCPM 동일 경매, oCPM 바닥가 가드레일과 함께 기존 oCPM 매출 잠식을 막는 1차 장치로 운영한다. 지면 매출 유지율 95% 이상은 이 장치가 작동하는지 검증하는 핵심 지표이며, 관련 수치와 임계값은 모두 파일럿 가정으로 운영 데이터에 따라 보정한다.
-수익 임팩트는 파일럿 지면의 월 1,000만 회 노출, 기존 oCPM 5,000원, 구매 전환 단가 4,000원, 평균 주문금액 40,000원, 거래 수수료율 7%, 광고 변동비 15%를 공통 가정으로 산정한다. 성과형 광고 기여 GMV는 oCPM으로는 유입되지 않던 신규 셀러가 만드는 증분 구매 GMV로 정의하며, 자연전환과 기존 oCPM 베이스라인에 포함된 GMV는 제외한다. 따라서 이 GMV에서 발생하는 거래 수수료는 기존 oCPM 베이스라인에 없던 순증분 기여로 계산한다. 파일럿에서는 대조군 기반 증분성 검증으로 이를 재산정한다. 이 비교는 지면 전체를 성과형으로 대체하는 경우가 아니라 성과형에 배정된 인벤토리 단위 기준이며, 전체 지면에서 성과형 매출 비중은 파일럿 5%와 확대 단계 10%를 목표로 한다.
-평가 기준은 광고 매출이 아니라 ‘에이블리 총 기여=광고비+광고 기여 GMV×거래 수수료율’로 둔다. 전환 1건당 거래 수수료 기여는 40,000원×7%=2,800원이며, 기존 oCPM 비교 기준은 광고 매출 5,000만원과 광고 변동비 차감 이익 4,250만원이다.
-시나리오  유효 전환율  공짜 소진율  광고비  광고 기여 GMV  거래 수수료  에이블리 총 기여  기존 oCPM 대비 총 기여 변화  총 기여 이익보수  0.11%  18%  3,608만원  4억 4,000만원  3,080만원  6,688만원  +34%  6,147만원
-기본  0.16%  10%  5,760만원  6억 4,000만원  4,480만원  1억 240만원  +105%  9,376만원
-낙관  0.21%  6%  7,896만원  8억 4,000만원  5,880만원  1억 3,776만원  +176%  1억 2,592만원
-총 기여 이익은 광고비에서만 변동비 15%를 차감하고 거래 수수료는 전액 반영한 파일럿 비교값이다. 기본 가정에서 신규 광고주 300명×월 평균 유효 전환 40건×전환 단가 4,000원은 월 광고비 4,800만원을 만든다. 같은 전환의 광고 기여 GMV는 4억 8,000만원이고 거래 수수료는 3,360만원이므로 월 에이블리 총 기여는 8,160만원이며, 30% 재집행 시 다음 달 총 기여 반복 기반은 2,448만원이다.
-총 기여 기준 손익분기 유효 전환율은 ‘기존 oCPM÷((전환 단가×(1-공짜 소진율)+평균 주문금액×거래 수수료율)×1,000)’으로 계산한다. 전환 단가 4,000원·평균 주문금액 40,000원·수수료율 7%·기존 oCPM 5,000원 기준으로 공짜 소진율 10%일 때 0.078%, 15%일 때 0.081%, 20%일 때 0.083% 이상이면 기존 oCPM 광고 매출을 초과하는 총 기여를 만든다. 파일럿 유효 전환율 목표 0.15%는 이 손익분기점을 충분히 상회하며, 거래 수수료를 제외한 광고비 기준으로도 공짜 소진율 10%의 손익분기점 0.139%를 넘어 지면 매출 유지율 95% 목표와 정합성을 갖는다. 수치는 파일럿 전 과거 지면별 전환율·주문금액·인벤토리 원가·환불률과 증분성 분석 결과로 재산정한다.</t>
+경험  광고 밀도·노출 점유율  추천 N개당 광고 1개 이하  상한 준수  상한 초과
+신규 한정·성과형 월 집행 상한·추천 N개당 광고 1개 밀도 캡·예상 eCPM 및 추천 적합도 최소 기준은 eCPM 동일 경매와 oCPM 바닥가 95%·80% 가드레일, 지면 매출 유지율 95%와 함께 기존 oCPM 매출 및 추천 경험을 지키는 장치다.
+수익 임팩트는 홈 개인화 추천 피드 기존 sponsored 슬롯의 월 1,000만 회 광고 노출, 기존 oCPM 5,000원, 발견 지면의 파일럿 유효 전환율 0.08%, 구매 전환 단가 4,000원, 평균 주문금액 40,000원, 거래 수수료율 7%, 광고 변동비 15%를 공통 가정으로 산정한다. 추천 피드는 검색보다 저의도 발견 지면이므로 기존 0.15% 목표 대신 0.08%를 보수적 출발 가정으로 사용한다. 순증분 전환은 holdout의 노출군과 미노출 유사 이용자군 전환 차이로 산정하며, 광고비·광고 기여 GMV·거래 수수료는 이 순증분분만 수익으로 인정한다.
+시나리오  관측 유효 전환율  holdout 증분 비율  순증분 전환율  순증분 광고비  순증분 광고 기여 GMV  거래 수수료  에이블리 총 기여보수  0.06%  50%  0.03%  120만원  1억 2,000만원  840만원  960만원
+기본  0.08%  60%  0.048%  192만원  1억 9,200만원  1,344만원  1,536만원
+낙관  0.10%  70%  0.07%  280만원  2억 8,000만원  1,960만원  2,240만원
+위 표는 성과형에 실제 배정된 기존 sponsored 슬롯 인벤토리 단위의 증분 기여이며, 전체 추천 피드를 성과형으로 대체한 값이 아니다. 기본 가정에서 순증분 전환 480건은 전환당 광고비 4,000원과 전환당 거래 수수료 2,800원을 합한 6,800원의 총 기여를 만든다. 기존 oCPM 기준 광고 매출 5,000만원과의 직접 비교는 성과형 배정 슬롯 비중, 광고 밀도 캡, 동일 경매 배분 및 holdout 결과를 반영해 산정하며, 전체 지면은 95% 이상의 매출 유지율을 지켜야 한다.
+총 기여 기준 손익분기 순증분 전환율은 ‘기존 oCPM 대비 성과형에 배정된 인벤토리 매출÷((전환 단가×(1-공짜 소진율)+평균 주문금액×거래 수수료율)×1,000)’으로 계산한다. 공짜 소진율 10%, 전환 단가 4,000원, 평균 주문금액 40,000원, 거래 수수료율 7%에서 전환 1건당 총 기여는 6,400원이며, 실제 손익분기는 성과형 배정 슬롯 비중과 holdout 순증분 비율을 함께 반영해 재산정한다. 파일럿 전에는 추천 피드 월 노출·sponsored 슬롯 수·실제 oCPM·전환율·주문금액·환불률·holdout 표본 크기로 모든 가정을 재검증한다.</t>
   </si>
   <si>
     <t>리스크</t>
   </si>
   <si>
-    <t>첫째, 전환이 발생하지 않는 상품이 상품광고 지면을 점유해 플랫폼이 무료 노출과 인벤토리 기회비용을 부담할 수 있다. 성과형 캠페인을 예상 전환율×전환 단가의 eCPM으로 환산해 oCPM과 동일 경매에서 경쟁시키고, 예상 eCPM이 지면별 oCPM 바닥가의 95% 미만이면 자동으로 우선순위를 낮추며 80% 미만이면 oCPM 캠페인으로 대체한다. 둘째, 전환 가능성이 낮은 광고주가 성과형 상품에 몰리는 역선택을 막기 위해 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주만 MVP 참여 대상으로 제한하고, 기존 품질 게이트와 성과형 월 집행 상한을 함께 적용한다. 이 신규 한정·집행 상한은 eCPM 동일 경매·바닥가 가드레일·지면 매출 유지율 95%와 함께 기존 oCPM 매출 잠식을 막는 1차 장치다. 셋째, 셀프 구매·쿠폰 반복 사용 등 가짜 전환은 결제자·기기·계정 중복 제거, 환불·취소 제외, 이상 패턴 탐지, 전환 검증 보류 및 정산 조정으로 방어한다. 넷째, 자연적으로 구매할 고객에게도 광고 기여를 인정하면 광고비와 거래 수수료의 증분 기여를 과대평가할 수 있으므로 클릭 후 기여 윈도우, 중복 제거, 자연전환과 광고 기여전환 구분 및 대조군 기반 증분성 분석을 적용한다. 다섯째, 성과형 상품이 기존 CPD·oCPM 매출을 잠식할 수 있으므로 대형 브랜드 CPD는 유지하고 MVP를 신규 중소 셀러와 한정 지면에 제한하며, 유효 전환 50건 달성 셀러에게는 oCPM 유상 광고 전환을 안내한다. 여섯째, Phase 2에서 소액 기존 중소 셀러로 확대할 때는 내부 머신러닝 학습 안정성과 운영 데이터를 기준으로 졸업 기준 상향을 검토하고, eCPM 경매와 집행 상한으로 잠식을 계속 방어한다. 일곱째, 외부 미입점 광고주는 거래 수수료가 발생하지 않아 순수 광고 수익과 인벤토리 수익성만으로 손익을 검증해야 하므로 입점 셀러 파일럿 이후 Phase 2에서 별도 기준으로 검토한다.</t>
+    <t>첫째, 저의도 발견 지면에서 성과형 광고가 무료 노출을 소진하거나 추천 경험을 해칠 수 있다. 홈 개인화 추천 피드 ‘○○님을 위��� 추천 상품’의 기존 sponsored 슬롯에서만 운영하고, 추천 상품 카드와 동일한 네이티브 UI·광고 라벨·추천 N개당 광고 1개 밀도 캡을 유지한다. 둘째, 신규 성과형은 추천 AI 예상 전환율×전환 단가의 eCPM과 추천 적합도·품질로 기존 oCPM과 동일 경매에서 경쟁하며, 예상 eCPM이 oCPM 바닥가의 95% 미만이면 우선순위를 낮추고 80% 미만이면 oCPM으로 대체한다. 셋째, 오가닉 추천과 광고 추천의 중복으로 성과가 과대평가될 수 있으므로 last-click 7일은 과금 귀속에만 사용하고, holdout 대조군 기반 순증분 전환만 수익 검증 및 정산 보정에 사용한다. 넷째, holdout 표본 부족·결과 지연·실험 오염은 증분성 판단을 왜곡할 수 있으므로 표본 충족 전 자동 확대·정산 보정을 막고, 실험 배정과 결과 산출을 감사 로그로 관리한다. 다섯째, 신규 광고주 한정·기존 품질 게이트·누적 유효 전환 50건 졸업·월 집행 상한은 대형 셀러 유입과 기존 oCPM 매출 잠식을 막는 장치다. 여섯째, 셀프 구매·쿠폰 반복 사용 등 가짜 전환은 멱등키, 결제자·기기·계정 중복 제거, D+7·D+14 검증, 환불·취소 제외로 방어한다. 일곱째, 외부 미입점 광고주는 거래 수수료가 발생하지 않으므로 입점 셀러 파일럿과 분리해 Phase 2에서 검토한다.</t>
   </si>
   <si>
     <t>카테고리</t>
@@ -159,11 +161,11 @@
     <t>1 순수 성과형 캠페인 생성 및 과금</t>
   </si>
   <si>
-    <t xml:space="preserve">입점 중소·신규 셀러가 기존 활성 광고 지면에 캠페인을 생성하고, 구매·쿠폰 사용·앱 설치 등 유효 전환이 발생한 경우에만 전환 단가 기준으로 비용을 지불하도록 한다. 광고 노출이나 클릭만 발생하고 전환이 없으면 과금하지 않는다. MVP에서는 신규 지면을 개발하지 않고 투데이 추천상품, 투데이·검색결과 유사 상품 추천, 상품상세 연관추천, 검색 기반 신규 지면에 과금 레이어를 적용한다. CPA 상한 보장과 전환 건수 보장은 Phase 2로 제외한다.
-1. ○ Given 참여 자격을 충족한 입점 셀러가 상품과 전환 유형을 선택했을 때, When 일일 또는 총예산과 기간을 입력해 검토를 요청하면, Then 플랫폼은 적용 전환 단가·예상 전환 수·예상 비용을 표시하고 초안 캠페인을 저장한다.
-2. ○ Given 심사를 통과한 캠페인이 집행 중일 때, When 노출 또는 클릭만 발생하면, Then 캠페인 비용은 0원으로 유지된다.
+    <t xml:space="preserve">신규 광고주가 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯에서 순수 성과형 캠페인을 만들고 관리할 수 있게 한다. 이 요구사항은 신규 지면 개발이 아니라 기존 sponsored 슬롯에 전환 과금 옵션을 추가하는 범위이며, 유효 전환 외 노출·클릭에는 비용을 청구하지 않는다. 추천 카드와 동일한 네이티브 UI·광고 라벨·밀도 캡은 포함하고, CPA 상한 보장과 전환 건수 보장은 제외한다.
+1. ○ Given 참여 자격을 충족한 신규 입점 셀러가 상품과 전환 유형을 선택했을 때, When 홈 개인화 추천 피드 sponsored 슬롯용 예산과 기간을 입력하면, Then 플랫폼은 적용 전환 단가·예상 전환 수·예상 비용을 표시하고 초안 캠페인을 저장한다.
+2. ○ Given 심사를 통과한 성과형 캠페인이 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 집행 중일 때, When 노출 또는 클릭만 발생하면, Then 캠페인 비용은 0원으로 유지된다.
 3. ○ Given 유효 전환이 확정되었을 때, When 누적 유효 전환 수가 50건에 도달하면, Then 성과 검증 완료로 기록하고 oCPM 유상 광고 전환을 안내하며 성과형 월 집행 상한을 적용한다.
-4. ○ Given 캠페인이 예산·노출 한도 또는 참여 제한에 도달했을 때, When 다음 노출 기회가 발생하면, Then 신규 노출을 제한하고 제한 사유를 기록한다.</t>
+4. ○ Given 캠페인이 예산·노출 한도·밀도 캡 또는 참여 제한에 도달했을 때, When 다음 추천 피드 노출 기회가 발생하면, Then 신규 노출을 제한하고 제한 사유를 기록한다.</t>
   </si>
   <si>
     <t>높음</t>
@@ -175,22 +177,19 @@
     <t>1.1 성과형 캠페인 생성 및 비용 관리</t>
   </si>
   <si>
-    <t xml:space="preserve">최근 N개월 유상 광고 집행 이력이 없는 입점 셀러가 참여 가능한 상품으로 순수 성과형 상품광고 캠페인을 만들고 예산·기간·전환 유형을 관리하는 기능이다. 유효 전환이 확정된 경우에만 비용을 누적하며, 노출·클릭만으로는 비용을 청구하지 않는다. 누적 유효 전환 50건을 달성한 셀러에게는 oCPM 유상 광고 전환을 안내하되 성과형 이용은 월 집행 상한 안에서 유지한다.
+    <t xml:space="preserve">최근 N개월 유상 광고 집행 이력이 없는 입점 셀러가 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯을 대상으로 순수 성과형 캠페인을 만들고 예산·기간·전환 유형을 관리하는 기능이다. 신규 지면을 만들지 않고 기존 sponsored 슬롯의 과금 옵션만 추가하며, 유효 전환이 확정된 경우에만 비용을 누적한다. 누적 유효 전환 50건 달성 후에는 oCPM 전환을 안내하되 성과형 이용은 월 집행 상한 안에서 유지한다.
 [기능의 근거] 선불 광고비와 성과 불확실성 때문에 상품광고를 시작하기 어려운 중소·신규 셀러가 성과 발생분만 비용을 내도록 지원한다.
 [성공 기준] 첫 캠페인 전환 발생률이 파일럿에서 35% 이상에 도달한다.
 [개발 준비 슬롯]
-• 선행조건: - 셀러가 입점 셀러이며 파일럿 참여 자격을 충족한다.
-• 선택한 상품이 판매 가능 재고와 품질 기준을 충족한다.
-• 카테고리·지면별 캠페인 한도가 남아 있다.
-• 내부 자격 평가, 단가 제시, 경매 엔진 및 정산 서비스가 사용 가능하다.
+• 선행조건: - 셀러가 신규 광고주·기존 품질 게이트를 충족하고 홈 개인화 추천 피드 sponsored 슬롯의 파일럿 대상에 포함된다.
+• 선택 상품이 추천 가능 재고·품질 기준과 추천 적합도 최소 기준을 충족한다.
+• 홈 개인화 추천 피드의 기존 sponsored 슬롯, 밀도 캡 및 경매 설정이 등록되어 있다.
 • 트리거: - 셀러가 셀러센터의 성과형 상품광고 시작 버튼을 선택한다.
 • 광고 운영자가 자격 충족 셀러에게 초대 링크를 발송한다.
-• 동작: - 셀러가 상품, MVP 전환 유형인 구매 또는 쿠폰 사용, 기간, 일일 또는 총예산을 입력한다.
-• 플랫폼이 카테고리 기준단가와 품질·예측값 및 상품가 구간 수익 가드를 반영한 적용 전환 단가를 80~120% 범위에서 제시한다.
-• 플랫폼이 예상 전환 수와 예상 비용을 계산해 검토 화면에 표시한다.
-• 셀러가 전환 과금·검증·환불 조정 기준에 동의하면 캠페인을 초안 또는 심사 상태로 저장한다.
-• 누적 유효 전환 수가 50건에 도달하면 플랫폼이 성과 검증 완료로 기록하고 oCPM 유상 광고 전환을 안내하며 성과형 이용은 유지한다.
-• FE는 입력·검토·상태 화면을 만들고 BE는 생성·예산·비용·졸업 상태를 처리하며 Data·ML은 예측값을 제공하고 정산은 확정 비용을 청구 대상으로 전달한다.
+• 동작: - 셀러가 홈 개인화 추천 피드 sponsored 슬롯용 상품, 구매 또는 쿠폰 사용 전환 유형, 기간, 일일 또는 총예산을 입력한다.
+• 플랫폼이 추천 AI 예측과 상품가 구간 수익 가드를 반영한 플랫폼 제시 전환 단가·예상 전환 수·예상 비용을 표시한다.
+• 셀러가 순수 성과형 과금과 last-click 검증 기준에 동의하면 캠페인을 초안 또는 심사 상태로 저장한다.
+• 플랫폼이 유효 전환 50건 달성 시 oCPM 전환을 안내하고 성과형 월 집행 상한을 적용한다.
 • 결과: - 캠페인, 예산, 적용 전환 단가 및 동의 기록을 저장한다.
 • 유효 전환이 확정될 때만 누적 비용, 잔여 예산 및 누적 유효 전환 수를 갱신한다.
 • 누적 유효 전환 수가 50건에 도달하면 캠페인·셀러 상태를 졸업으로 전이하고 성과형 월 집행 상한을 적용한다.
@@ -199,12 +198,9 @@
 • 예산 소진 중 발생한 전환은 전환 발생 시점의 집행 가능 여부와 확정 규칙을 기준으로 비용을 처리한다.
 • 심사 중 상품이 품절되거나 참여 자격이 상실되면 캠페인을 제한 상태로 전환한다.
 • 단가·예측 서비스가 응답하지 않으면 캠페인 시작을 막고 재시도 안내를 표시한다.
-• 표시: - 생성 화면은 상품 선택, 전환 유형, 예산·기간 입력, 단가·예상 성과 검토 순서로 표시한다.
-• 생성 화면은 상품가 구간 또는 카테고리 평균 주문금액에 따른 참여 제한·단가 조정 사유를 표시한다.
-• 비용이 발생하지 않은 노출·클릭은 0원 과금으로 안내한다.
-• 제한 상태에는 제한 사유와 조정 가능한 상품·예산 안내를 표시한다.
-• 누적 유효 전환 수가 졸업 대기 구간에 진입하면 성과 검증 진행 상태와 oCPM 전환 준비 안내를 표시한다.
-• 졸업 상태에는 oCPM 유상 광고 전환 안내와 성과형 월 집행 상한 적용 사실을 표시한다.
+• 표시: - 생성 화면은 홈 개인화 추천 피드의 기존 광고 슬롯에서 노출되는 상품임을 표시한다.
+• 생성 화면은 추천 상품 카드와 같은 네이티브 UI 및 광고 라벨이 사용자 화면에 유지됨을 안내한다.
+• 생성 화면은 노출·클릭만으로는 비용이 발생하지 않고 유효 전환 확정 시에만 과금됨을 표시한다.
 • 권한 &amp; 접근: - 광고주·입점 셀러는 자기 사업자 소유 상품의 캠페인만 생성·수정할 수 있다.
 • 광고 운영자는 운영 권한 범위에서 심사와 제한 처리를 할 수 있다.
 • 비즈니스 규칙: - MVP의 전환 유형은 구매와 쿠폰 사용이며 앱 설치는 해당 캠페인에 한해 별도 승인 후 적용하거나 Phase 2에서 도입한다.
@@ -213,10 +209,9 @@
 • 카테고리 평균 주문금액과 수수료 기여가 파일럿 수익 가정에 미달하면 상품가 구간별 전환 단가를 조정하거나 참여를 제한한다.
 • 캠페인은 예산, 셀러당 일일 노출 한도, 카테고리 참여 제한 및 졸업 후 성과형 월 집행 상한을 넘겨 집행할 수 없다.
 • 누적 유효 전환 50건은 성과 검증 완료와 oCPM 유상 광고 전환 안내의 파일럿 기준이며, 내부 머신러닝 최소 학습 전환 기준과 운영 데이터로 보정한다.
-• 데이터: - 캠페인은 campaignId, sellerId, 상품Id, 전환유형, 상태, 시작·종료일, 일일예산, 총예산, 적용전환단가, 누적비용, 잔여예산, 누적유효전환수, 졸업상태, 졸업일시, 성과형월집행상한을 가진다.
-• 캠페인 상태는 신규-성과형, 졸업 대기, 졸업, 초안, 심사, 집행중, 제한, 중단을 포함한다.
-• 캠페인 생성 요청은 requestId를 유일값으로 저장한다.
-• 비용은 원화 정수 금액으로 저장한다.</t>
+• 데이터: - 캠페인은 placementKey, billingModel, 광고라벨버전, 밀도캡버전 및 추천적합도최소기준버전을 추가로 가진다.
+• placementKey는 홈 개인화 추천 피드의 기존 sponsored 슬롯을 식별한다.
+• billingModel은 신규 성과형 또는 기존 oCPM 중 하나로 저장한다.</t>
   </si>
   <si>
     <t>광고주·입점 셀러, 광고 운영자</t>
@@ -225,17 +220,17 @@
     <t>2 전환 측정 및 어트리뷰션</t>
   </si>
   <si>
-    <t xml:space="preserve">에이블리 내부 결제·쿠폰 사용 로그와 외부 전환 API·포스트백을 연동해 광고 기여 전환을 측정한다. 클릭 후 전환 기여 윈도우를 적용하고, 동일 사용자의 중복 전환을 제거하며, 자연전환과 광고 기여전환을 구분한다.
-1. ○ Given 내부 구매 또는 쿠폰 사용 로그가 수신되었을 때, When 클릭 후 기여 윈도우 안의 이벤트가 중복 제거를 통과하면, Then 해당 이벤트를 잠정 전환으로 집계한다.
+    <t xml:space="preserve">내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백으로 last-click 7일 기준의 과금 귀속 전환을 수집·검증하고, 홈 추천 피드 광고의 순증분 효과를 holdout 대조군으로 측정한다. last-click은 과금 귀속용이며 view-through는 제외한다. holdout은 광고가 없었어도 오가닉 추천으로 발생했을 전환을 제외하기 위한 증분 검증·정산 보정용으로, 과금 귀속과 구분한다.
+1. ○ Given 내부 구매 또는 쿠폰 사용 로그가 수신되었을 때, When 클릭 후 7일 안의 이벤트가 멱등키 중복 제거를 통과하면, Then 해당 이벤트를 마지막 유효 클릭 기준 잠정 과금 전환으로 집계한다.
 2. ○ Given 외부 광고주가 전환 API 또는 포스트백을 호출했을 때, When 필수 필드와 멱등키가 유효하면, Then 중복 없이 잠정 전환을 저장하고 수신 결과를 반환한다.
-3. ○ Given 잠정 전환이 검증 기한에 도달했을 때, When 취소·환불·부정 거래·정책 위반이 없으면, Then 내부 전환은 D+7, 외부 전환은 D+14에 유효 전환으로 확정한다.
-4. ○ Given 확정된 주문이 취소 또는 환불되었을 때, When 정산 조정이 실행되면, Then 해당 전환을 무효 또는 환불 차감으로 반영하고 다음 청구서 조정 내역을 생성한다.</t>
+3. ○ Given 홈 추천 피드의 성과형 캠페인이 holdout 실험 대상일 때, When 노출군과 미노출 유사 이용자군의 검증 기간 전환을 비교하면, Then 순증분 전환 수·증분 전환율·신뢰도·표본 충족 상태를 저장한다.
+4. ○ Given 잠정 전환이 검증 기한에 도달했을 때, When 취소·환불·부정 거래·정책 위반이 없으면, Then 내부 전환은 D+7, 외부 전환은 D+14에 유효 전환으로 확정하고 holdout 결과에 따라 정산 보정 대상으로 표시한다.</t>
   </si>
   <si>
     <t>2.1 전환 수집 및 검증</t>
   </si>
   <si>
-    <t xml:space="preserve">내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백에서 마지막 유효 클릭 기준의 광고 기여 전환을 수집하고 검증하는 기능이다. MVP에서는 클릭 기여만 인정하고 노출만 발생한 view-through 기여와 앱 설치 전환은 제외하며, 기여 윈도우·중복 제거·환불·취소 및 부정 거래 규칙을 적용해 유효 전환만 과금·정산에 전달한다.
+    <t xml:space="preserve">홈 개인화 추천 피드 sponsored 슬롯의 내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백에서 마지막 유효 클릭 기준 과금 전환을 수집·검증하고, holdout 대조군의 순증분 전환 산정에 필요한 원천 데이터를 제공하는 기능이다. MVP에서는 클릭 기여만 과금하며 view-through 기여와 앱 설치 전환은 제외한다. last-click 7일은 과금 귀속용이고 holdout 결과는 증분 검증·정산 보정용으로 분리한다.
 [기능의 근거] 광고주는 실제 성과에만 비용을 낸다는 신뢰가 필요하고, 플랫폼은 잘못된 전환 과금과 자연전환 과대평가를 방지해야 한다.
 [성공 기준] 유효 전환율이 파일럿에서 0.15% 이상이고 전환 예측 오차가 절대오차 20% 이하를 유지한다.
 [개발 준비 슬롯]
@@ -245,14 +240,12 @@
 • 트리거: - 내부 구매·쿠폰 사용 이벤트가 발생한다.
 • 외부 광고주가 전환 API 또는 포스트백을 호출한다.
 • D+7 또는 D+14 검증 작업과 환불·취소 조정 작업이 실행된다.
-• 동작: - 플랫폼이 전환 이벤트의 캠페인·사용자 연계를 확인하고 기여 윈도우 안의 마지막 유효 클릭 1건을 선택한다.
-• 플랫폼이 주문·쿠폰 사용 이벤트와 멱등키로 중복을 제거한 뒤 선택된 마지막 유효 클릭의 캠페인에만 잠정 전환으로 저장한다.
-• 플랫폼은 노출만 발생한 view-through 기여를 MVP 과금·정산 대상에서 제외한다.
-• 내부 전환은 D+7, 외부 전환은 D+14에 취소·환불·부정 거래 여부를 검증한다.
-• FE는 전환 근거와 상태 조회를 제공하고 BE는 수집·검증·중복 제거를 처리하며 Data·ML은 이상 탐지 신호를 제공하고 정산은 확정·조정 결과를 반영한다.
-• 결과: - 잠정·확정·무효·환불 차감 상태의 전환 이벤트를 저장한다.
-• 확정 전환만 캠페인 비용과 정산 내역에 반영한다.
-• conversionreceived, conversionconfirmed, conversion_invalidated 이벤트를 기록한다.
+• 동작: - 플랫폼이 클릭 후 7일 기여 윈도우의 마지막 유효 클릭을 선택해 잠정 과금 전환으로 저장한다.
+• 플랫폼이 노출 로그와 사용자 비식별키를 holdout 측정에 전달하되, holdout 결과를 last-click 과금 귀속에 직접 대체하지 않는다.
+• 플랫폼이 내부 전환은 D+7, 외부 전환은 D+14에 확정하고 확정 결과를 증분성 정산 보정 후보와 연결한다.
+• 결과: - 과금 전환에는 last-click 귀속 근거와 검증 상태를 저장한다.
+• holdout 측정용 노출·클릭·전환 원천 이벤트는 실험 배정 식별자와 함께 저장한다.
+• 정산 보정 후보에는 증분성 결과 버전과 적용 상태를 기록한다.
 • 예외: - 동일 멱등키 또는 동일 주문·쿠폰 사용 이벤트는 한 번만 집계한다.
 • 한 전환에 복수 광고 클릭이 있으면 기여 윈도우 안의 마지막 유효 클릭 1건에만 귀속한다.
 • 기여 윈도우 종료 시각 경계의 이벤트는 발생 시각과 마지막 유효 클릭 시각을 기준으로 판정한다.
@@ -269,9 +262,9 @@
 • 취소·환불·부정 거래·셀프 구매·정책 위반 전환은 과금 대상에서 제외한다.
 • 내부 전환은 D+7, 외부 전환은 D+14에 유효 여부를 확정한다.
 • 앱 설치 전환은 해당 캠페인에 한해 별도 승인 후 적용하거나 Phase 2에서 도입한다.
-• 데이터: - 전환 이벤트는 conversionId, idempotencyKey, campaignId, 전환유형, 원이벤트Id, 발생시각, 수신시각, 마지막유효클릭Id, 검증상태, 무효사유, 적용단가를 가진다.
-• 내부 주문·쿠폰 원본 식별자는 접근 통제된 참조값으로 저장한다.
-• idempotencyKey는 전환 소스와 원이벤트 식별자를 조합한 유일값이다.</t>
+• 데이터: - 전환 이벤트는 placementKey, 광고노출Id, holdoutExperimentId, holdoutCohort, 정산보정상태를 추가로 가진다.
+• holdoutCohort는 노출군, 미노출 대조군 또는 실험 제외 중 하나로 저장한다.
+• 사용자 식별자는 holdout 산정에 필요한 비식별 키로만 저장하고 광고주 화면에 제공하지 않는다.</t>
   </si>
   <si>
     <t>광고 운영자, 데이터·분석 담당자, 정산·고객지원 담당자</t>
@@ -280,58 +273,97 @@
     <t>Web, Desktop</t>
   </si>
   <si>
+    <t>2.2 holdout 증분성 측정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">홈 개인화 추천 피드의 성과형 sponsored 슬롯이 오가닉 추천 대비 실제로 만든 순증분 전환을 holdout 대조군으로 측정하는 기능이다. 노출군과 광고를 노출하지 않는 유사 이용자군의 전환 차이를 산정해 수익 검증과 정산 보정에 사용한다. last-click 과금 귀속을 대체하지 않으며, 표본과 신뢰도가 부족한 결과는 자동 확대·정산 보정에서 제외한다.
+[기능의 근거] 발견 지면에서는 광고가 없었어도 오가닉 추천으로 발생했을 전환이 존재하므로, 과금 전환만으로 광고의 순증분 가치를 판단하면 광고 기여와 거래 수수료를 과대평가할 수 있다.
+[성공 기준] holdout 결과에서 증분 전환율이 양수이고, 표본 충족·신뢰도 기준을 만족한 캠페인 비율을 파일럿 확대 판단에 활용한다.
+[개발 준비 슬롯]
+• 선행조건: - 홈 개인화 추천 피드의 기존 sponsored 슬롯 노출·클릭·전환 로그가 사용자 비식별키와 함께 수집된다.
+• 실험 대상 캠페인, 대상 기간, 노출군과 미노출 대조군 배정 규칙이 등록된다.
+• 내부 전환 D+7 및 외부 전환 D+14 검증 결과를 조회할 수 있다.
+• 트리거: - 관리자가 캠페인 또는 슬롯 단위 holdout 실험을 승인한다.
+• 실험 배정 시점에 홈 개인화 추천 피드 sponsored 슬롯 노출 기회가 발생한다.
+• 실험 종료 또는 표본 충족 시 증분성 산출 작업이 실행된다.
+• 동작: - 플랫폼이 적격 이용자를 노출군 또는 미노출 유사 대조군으로 배정하고 배정 결과를 저장한다.
+• 노출군에는 기존 경매 결과에 따른 sponsored 광고를 노출하고 대조군에는 해당 광고를 노출하지 않는다.
+• 플랫폼이 검증 완료 전환을 집계해 노출군과 대조군의 전환 차이로 순증분 전환·증분 전환율·신뢰도를 산정한다.
+• 플랫폼이 표본·신뢰도 기준을 충족한 결과만 수익 검증과 정산 보정 후보로 전달한다.
+• 결과: - 실험별 노출군·대조군 규모, 전환 수, 순증분 전환 수, 증분 전환율, 신뢰도, 표본 충족 상태를 저장한다.
+• 표본과 신뢰도가 충족된 결과만 정산 보정 후보와 파일럿 확대 판단에 연결한다.
+• holdoutassigned, incrementalitycalculated, incrementalityqualified, incrementalitydelayed 이벤트를 기록한다.
+• 예외: - 실험군 간 사용자 중복 또는 노출 오염이 탐지되면 해당 사용자를 분석 대상에서 제외하고 오염 사유를 기록한다.
+• 전환 검증이 완료되지 않았거나 결과 지연이 발생하면 증분성 결과를 잠정 상태로 표시하고 정산 보정을 막는다.
+• 표본이 목표에 미달하거나 신뢰도 기준을 충족하지 못하면 자동 확대와 정산 보정을 막고 재측정을 요청한다.
+• 개인정보 접근 권한이 없는 사용자는 사용자 단위 배정·전환 원본을 조회할 수 없다.
+• 표시: - 운영자 화면은 실험 대상, 기간, 노출군·대조군 표본, 전환 차이, 순증분 전환, 신뢰도, 오염률, 결과 지연 및 정산 보정 상태를 표시한다.
+• 광고주 화면은 캠페인 단위 순증분 전환·증분 전환율·산출 상태만 집계값으로 표시하고 실험 배정 정보는 제공하지 않는다.
+• 표본 미달 또는 신뢰도 미충족 상태에는 확대·정산 보정에 사용되지 않음을 표시한다.
+• 권한 &amp; 접근: - 플랫폼 관리자만 holdout 대상·기간·배정 규칙과 정산 보정 적용을 변경할 수 있다.
+• 데이터·분석 담당자는 비식별 실험 원천 데이터와 결과를 조회할 수 있다.
+• 정산·고객지원 담당자는 확정된 집계 결과와 정산 보정 상태만 조회할 수 있다.
+• 광고주는 자기 캠페인의 집계 결과만 조회할 수 있다.
+• 비즈니스 규칙: - holdout은 오가닉 추천으로 발생했을 전환을 제외한 순증분 전환 측정용이며 last-click 7일 과금 귀속을 대체하지 않는다.
+• 대조군에는 동일 sponsored 광고를 노출하지 않되, 오가닉 추천 경험은 유지한다.
+• 증분성 결과는 표본 충족과 신뢰도 기준을 만족한 경우에만 수익 검증·정산 보정·확대 판단에 사용한다.
+• holdout 결과가 미달 또는 지연된 경우 과금 전환은 기존 last-click 7일 및 D+7·D+14 확정 정책으로 처리한다.
+• 데이터: - holdout 실험은 experimentId, placementKey, campaignId, 시작·종료일, 배정규칙버전, 노출군비율, 대조군비율, 상태, 결과버전을 가진다.
+• 실험 배정은 experimentId, 사용자비식별키, cohort, 배정시각, 제외사유를 가진다.
+• 증분성 결과는 experimentId, 기준기간, 노출군표본수, 대조군표본수, 노출군전환수, 대조군전환수, 순증분전환수, 증분전환율, 신뢰도, 오염률, 표본충족여부, 결과상태, 정산보정상태를 가진다.
+• 정산 보정 기록은 adjustmentId, experimentId, campaignId, 적용기간, 보정기준, 보정금액, 승인자, 상태를 가진다.</t>
+  </si>
+  <si>
+    <t>기획 작성중</t>
+  </si>
+  <si>
+    <t>플랫폼 관리자, 데이터·분석 담당자, 정산·고객지원 담당자</t>
+  </si>
+  <si>
     <t>3 타겟팅·성과 예측·품질 방어</t>
   </si>
   <si>
-    <t xml:space="preserve">상품 카테고리, 가격대, 사용자 행동, 검색·탐색 관심사, 과거 구매 및 전환 데이터를 활용해 광고 타겟을 구성하고 전환 가능성을 예측한다. 전환이 활발한 카테고리와 지면을 우선 제공하며, 저품질 상품·셀러 및 어뷰징 가능성이 높은 캠페인을 제한한다.
+    <t xml:space="preserve">추천 AI의 사용자·상품 맥락별 예상 전환율과 추천 적합도를 활용해 신규 성과형 광고의 참여 자격·노출 순위·품질 방어를 결정한다. 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 성과형과 기존 oCPM은 동일 경매로 경쟁한다. 예상 eCPM·추천 적합도·품질 최소 기준에 못 미친 캠페인은 노출하지 않아 공짜 소진과 추천 경험 훼손을 방어한다.
 1. ○ Given 셀러와 상품의 최근 90일 판매·평점·재고·배송 품질 및 유상 광고 집행 이력이 있을 때, When 참여 자격을 평가하면, Then 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주 여부와 기존 품질 기준 충족 여부 및 제한 사유를 저장한다.
-2. ○ Given 집행 가능한 캠페인이 있을 때, When 지면 경매가 발생하면, Then 예상 전환율과 플랫폼 제시 전환 단가를 사용해 eCPM을 계산한다.
-3. ○ Given 예상 eCPM이 지면별 oCPM 바닥가의 95% 미만일 때, When 노출 우선순위를 산정하면, Then 해당 캠페인의 우선순위를 낮춘다.
-4. ○ Given 동일 계정·기기·결제수단의 반복 전환 또는 비정상 패턴이 탐지되었을 때, When 위험도 기준을 초과하면, Then 전환을 검증 보류하거나 캠페인을 제한하고 근거를 기록한다.</t>
+2. ○ Given 홈 개인화 추천 피드 sponsored 슬롯의 경매가 발생하면, When 신규 성과형 캠페인을 평가하면, Then 추천 AI 예상 전환율×플랫폼 제시 전환 단가로 eCPM을 계산하고 추천 적합도·품질 점수를 함께 산정한다.
+3. ○ Given 신규 성과형과 기존 oCPM 캠페인이 같은 sponsored 슬롯에 참여할 때, When eCPM·추천 적합도·품질 랭킹을 산정하면, Then oCPM 바닥가 95%와 80% 가드레일을 적용해 성과형 노출 또는 oCPM 대체를 결정한다.
+4. ○ Given 예상 eCPM·추천 적합도·품질 중 하나가 최소 기준에 미달할 때, When 노출 기회를 평가하면, Then 광고를 노출하지 않고 제한 사유를 기록한다.</t>
   </si>
   <si>
     <t>3.1 참여 자격 평가와 경매 품질 방어</t>
   </si>
   <si>
-    <t xml:space="preserve">셀러·상품 품질, 유상 광고 집행 이력, 상품가 구간과 예상 전환율을 평가해 파일럿 참여 자격, 노출 우선순위 및 이상 전환 방어를 결정하는 기능이다. MVP에서는 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주만 참여시키고, 기존 품질 게이트를 유지한다. 누적 유효 전환 50건 달성 셀러는 졸업 상태로 전이해 oCPM 전환을 안내하고 성과형 월 집행 상한으로 대형 셀러 유입을 제한한다.
+    <t xml:space="preserve">추천 AI의 사용자·상품 맥락별 예상 전환율과 추천 적합도, 셀러·상품 품질을 평가해 홈 개인화 추천 피드 기존 sponsored 슬롯에서 신규 성과형 광고와 기존 oCPM 광고의 노출 순위를 결정하는 기능이다. 신규 성과형은 예상 전환율×플랫폼 제시 전환 단가의 eCPM으로 환산해 동일 경매에서 경쟁한다. 예상 eCPM·추천 적합도·품질이 최소 기준에 못 미치면 광고를 노출하지 않으며, 기존 95%·80% oCPM 바닥가 가드레일을 유지한다.
 [기능의 근거] 전환 가능성이 낮은 캠페인의 무료 노출 소진과 기존 oCPM 매출 기회비용을 방어해야 한다.
 [성공 기준] 공짜 소진율을 파일럿에서 15% 이하로 유지한다.
 [개발 준비 슬롯]
-• 선행조건: - 셀러의 최근 90일 주문, 상품 평점, 품절률, 배송 품질 및 정책 위반 이력이 조회 가능하다.
-• 셀러의 최근 N개월 유상 광고 집행 이력이 내부 광고 집행 기준으로 조회 가능하다.
-• 상품·셀러·지면·사용자 맥락별 예상 전환율과 품질 점수가 제공된다.
-• 경매 엔진이 oCPM 바닥가와 캠페인 노출 한도를 조회할 수 있다.
+• 선행조건: - 홈 개인화 추천 피드의 사용자·상품 맥락별 추천 적합도와 예상 전환율이 조회 가능하다.
+• 기존 sponsored 슬롯의 oCPM 바닥가, 광고 밀도 캡 및 현재 광고 점유율이 조회 가능하다.
 • 트리거: - 셀러가 참여 자격 심사를 요청한다.
 • 지면 경매 또는 일일 가드레일 평가가 실행된다.
 • 반복 클릭·자기 구매·쿠폰 악용 등 이상 신호가 수신된다.
-• 동작: - 플랫폼이 셀러·상품 데이터, 유상 광고 집행 이력 및 카테고리 평균 주문금액·예상 거래 수수료 기여를 기준으로 파일럿 참여 적합성과 제한 사유를 산정한다.
-• 플랫폼이 최근 N개월 유상 광고 집행 이력이 0원인 셀러를 신규 광고주로 판정하고, 별도 매출·거래액 증빙 서류는 요구하지 않는다.
-• 플랫폼이 예상 전환율×플랫폼 제시 전환 단가×1,000으로 MVP 경매 eCPM을 계산한다.
-• 플랫폼이 eCPM과 품질 점수로 oCPM 캠페인과 동일 지면의 랭킹을 산정한다.
-• FE는 자격·제한 안내를 표시하고 BE는 평가·한도를 집행하며 Data·ML은 예측·이상 탐지를 제공하고 정산은 보류 전환을 비용에서 제외한다.
-• 결과: - 셀러 참여 자격, 품질 점수, 예상 전환율, 평균 주문금액, 예상 수수료 기여, 노출 제한 상태와 사유를 저장한다.
-• eCPM 하회, 수익 가드 미충족 또는 이상 위험 캠페인의 노출을 축소하거나 전환 검증을 보류한다.
-• eligibilityevaluated, revenueguardlimited, auctionlimited, abuse_flagged 이벤트를 기록한다.
+• 동작: - 플랫폼이 추천 AI 예상 전환율×플랫폼 제시 전환 단가×1,000으로 신규 성과형 eCPM을 계산한다.
+• 플랫폼이 신규 성과형과 기존 oCPM을 같은 홈 추천 피드 sponsored 슬롯 경매에 참여시킨다.
+• 플랫폼이 eCPM, 추천 적합도 및 품질 점수로 랭킹하고 최소 기준 미달 캠페인은 광고를 노출하지 않는다.
+• 플랫폼이 추천 N개당 광고 1개 밀도 캡과 지면별 광고 점유율 상한을 적용한다.
+• 결과: - 경매 결과에 슬롯 식별자, 과금 방식, eCPM, 추천 적합도, 품질 점수, 노출·미노출 사유를 저장한다.
+• 추천 적합도·eCPM·품질 최소 기준 미달 또는 밀도 캡 초과 캠페인은 미노출로 기록한다.
 • 예외: - 예측 데이터가 부족한 신규 상품은 파일럿 참여 기준을 충족해도 보수적 노출 한도를 적용한다.
 • 실제 eCPM이 예상 eCPM의 80% 미만으로 3일 연속 하락하면 일일 노출 한도를 50% 축소한다.
 • 동일 계정·기기·결제수단의 반복 전환은 이상 탐지 대상으로 전환 검증을 보류한다.
 • 모델 또는 경매 엔진 장애 시 성과형 캠페인 신규 노출을 중단하고 oCPM 경매를 유지한다.
-• 표시: - 광고주에게 예상 eCPM, 실제 eCPM, 노출 제한 상태와 제한 사유를 표시한다.
-• 제한 캠페인에는 상품 품질·전환 단가·예산 조정 안내를 표시한다.
+• 표시: - 광고 노출 상품은 오가닉 추천 상품 카드와 동일한 네이티브 형식을 유지하고 광고 라벨을 표시한다.
+• 광고주에게는 추천 적합도 또는 eCPM 최소 기준 미달에 따른 미노출 사유를 표시한다.
 • 권한 &amp; 접근: - 광고 운영자와 플랫폼 관리자만 자격 기준·노출 한도·품질 제한을 변경할 수 있다.
 • 광고주는 자기 캠페인의 제한 결과와 개선 안내만 조회할 수 있다.
-• 비즈니스 규칙: - MVP의 적용 전환 단가는 카테고리 기준단가의 80~120% 범위에서 자동 조정한다.
-• MVP 참여 대상은 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주이며, 에이블리 기존 신규 광고주·무상 광고비 판정과 동일한 내부 광고 집행 이력 기준을 사용한다.
-• 최근 90일 주문 30건 이상, 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 기준은 신규 판정과 별도로 모두 충족해야 한다.
-• 카테고리 평균 주문금액 40,000원과 거래 수수료율 7%는 파일럿 수익 가정으로 모니터링한다.
-• 카테고리 평균 주문금액 또는 예상 거래 수수료 기여가 수익 가드 기준에 미달하면 상품가 구간별 전환 단가를 조정하거나 참여를 제한한다.
-• 예상 eCPM이 oCPM 바닥가의 95% 미만이면 우선순위를 낮추고 80% 미만이면 oCPM 캠페인으로 대체한다.
-• 셀러당 일일 노출 한도는 파일럿에서 지면 일일 노출의 5% 이하이다.
+• 비즈니스 규칙: - 신규 성과형과 기존 oCPM은 홈 개인화 추천 피드의 같은 sponsored 슬롯에서 동일 경매로 경쟁한다.
+• 신규 성과형 랭킹은 eCPM, 추천 적합도, 품질 점수를 함께 반영한다.
+• 예상 eCPM이 oCPM 바닥가의 95% 미만이면 우선순위를 낮추고 80% 미만이면 기존 oCPM 캠페인으로 대체한다.
+• 추천 피드는 추천 N개당 광고 1개 이하의 밀도 캡을 적용한다.
+• 예상 eCPM·추천 적합도·품질 중 하나라도 최소 기준에 미달하면 광고를 노출하지 않는다.
 • Phase 2 목표 CPA 입찰에서는 광고주 입찰 전환 단가가 eCPM의 직접 변수로 추가된다.
-• 데이터: - 참여 자격은 sellerId, 평가일, 주문수, 평점, 품절률, 배송품질, 유상광고집행이력플래그, 평균주문금액, 예상수수료기여, 수익가드판정, 적격여부, 제한사유를 가진다.
-• 유상광고집행이력플래그는 해당 없음, 소액, 일반 중 하나로 저장한다.
-• 예측 결과는 campaignId, 지면Id, 예상전환율, 품질점수, 예상eCPM, 모델버전, 산정시각을 가진다.
-• 이상 탐지 기록은 탐지Id, 전환Id, 위험유형, 위험점수, 처리상태를 가진다.</t>
+• 데이터: - 경매 후보는 placementKey, requestId, campaignId, billingModel, 예상전환율, 추천적합도, 품질점수, eCPM, oCPM바닥가, 밀도캡판정, 노출결과, 미노출사유, 모델버전, 산정시각을 가진다.
+• 광고 노출 로그는 노출Id, placementKey, 광고라벨표시여부, 피드순서, 사용자비식별키, 캠페인Id, 과금방식을 가진다.</t>
   </si>
   <si>
     <t>광고 운영자, 데이터·분석 담당자, 플랫폼 관리자</t>
@@ -340,17 +372,17 @@
     <t>4 광고주 성과 대시보드</t>
   </si>
   <si>
-    <t xml:space="preserve">광고주가 캠페인 성과와 과금 근거를 쉽게 이해하고 예산·상품·타겟을 조정할 수 있도록 전환 중심의 성과 대시보드를 제공한다. 광고비가 발생하지 않은 노출과 실제 과금된 전환을 명확히 구분한다.
-1. ○ Given 광고주가 권한 있는 캠페인을 조회할 때, When 기간·상품·지면·전환 유형 필터를 적용하면, Then 노출·클릭·잠정 및 확정 전환·전환당 비용·누적 비용·잔여 예산을 반환한다.
-2. ○ Given 전환이 발생하지 않은 기간일 때, When 성과 요약을 표시하면, Then 과금액 0원과 해당 기간의 노출·클릭 지표를 구분해 표시한다.
-3. ○ Given 과금된 전환을 선택했을 때, When 전환 근거를 조회하면, Then 전환 유형·발생 시각·검증 상태·적용 단가·조정 사유를 표시한다.
-4. ○ Given 예산 소진·품질 제한·전환 급증 또는 급감이 감지되었을 때, When 알림 조건을 충족하면, Then 광고주에게 원인과 다음 조치 안내를 제공한다.</t>
+    <t xml:space="preserve">광고주와 운영자가 홈 추천 피드 성과형 캠페인의 과금 전환, holdout 기반 순증분 전환, 오가닉 추천 잠식, 신규 고객 획득 및 밀도·점유율을 함께 확인할 수 있게 한다. 과금 귀속 지표와 증분성 검증 지표의 목적·집계 지연·보정 상태를 명확히 구분한다. 개인 식별 정보와 holdout 대상 배정 정보는 광고주에게 노출하지 않는다.
+1. ○ Given 광고주가 권한 있는 캠페인을 조회할 때, When 기간·상품·홈 추천 피드 sponsored 슬롯·전환 유형 필터를 적용하면, Then 노출·클릭·잠정 및 확정 전환·전환당 비용·누적 비용·잔여 예산을 반환한다.
+2. ○ Given holdout 결과가 산출되었을 때, When 광고주 또는 운영자가 증분성 지표를 조회하면, Then 순증분 전환·증분 전환율·오가닉 추천 잠식률·신규 고객 획득 수와 산출 상태를 분리해 표시한다.
+3. ○ Given 전환이 발생하지 않은 기간일 때, When 성과 요약을 표시하면, Then 과금액 0원과 해당 기간의 노출·클릭·holdout 집계 상태를 구분해 표시한다.
+4. ○ Given 과금된 전환 또는 증분성 집계를 선택했을 때, When 근거를 조회하면, Then last-click 과금 귀속 또는 holdout 정산 보정 중 적용 방식·검증 상태·조정 사유를 표시한다.</t>
   </si>
   <si>
     <t>4.1 전환 중심 성과 대시보드</t>
   </si>
   <si>
-    <t xml:space="preserve">광고주가 캠페인의 노출·전환·비용·예산과 과금 근거를 전환 중심으로 확인하고 상품·예산을 조정하는 기능이다. 자연전환과 광고 기여전환, 잠정과 확정 전환, 0원 과금 노출을 명확히 구분한다.
+    <t xml:space="preserve">광고주가 홈 개인화 추천 피드 sponsored 슬롯 성과형 캠페인의 노출·과금 전환·비용·예산과 holdout 기반 순증분 성과를 분리해 확인하는 기능이다. last-click 7일 과금 귀속과 holdout 증분 검증·정산 보정의 역할을 명확히 구분한다. 오가닉 추천 잠식률, 신규 고객 도달·획득 수, 광고 밀도·점유율은 광고주와 운영자 권한에 맞춰 제공한다.
 [기능의 근거] 광고주는 성과와 비용 산정 근거를 이해해야 재집행할 수 있다.
 [성공 기준] 파일럿 30일 재집행률이 30% 이상에 도달한다.
 [개발 준비 슬롯]
@@ -359,42 +391,41 @@
 • 트리거: - 광고주가 셀러센터에서 성과 대시보드를 연다.
 • 광고주가 기간·상품·카테고리·지면·전환 유형 필터를 변경한다.
 • 예산 소진·품질 제한·성과 급변 알림이 발생한다.
-• 동작: - 플랫폼이 필터 기준으로 노출, 클릭, 잠정·확정 전환, 전환율, 전환당 비용, 누적 비용, 잔여 예산을 조회한다.
-• 플랫폼이 과금 전환의 유형·시각·검증 상태·단가·조��� 사유를 상세 조회로 제공한다.
-• 플랫폼이 자연전환과 광고 기여전환을 분리해 표시한다.
-• FE는 요약·필터·상세·알림 화면을 만들고 BE는 집계·권한 조회를 제공하며 Data·ML은 예측 대비 성과를 공급하고 정산은 확정 비용·조정 내역을 제공한다.
+• 동작: - 플랫폼이 홈 추천 피드 sponsored 슬롯의 과금 전환·비용 지표와 holdout 기반 순증분 전환·증분 전환율을 분리 집계한다.
+• 플랫폼이 오가닉 추천 잠식률, 신규 고객 도달·획득 수, 광고 밀도·점유율을 산출한다.
+• 플랫폼이 last-click 과금 귀속과 holdout 정산 보정의 적용 상태·집계 지연·신뢰도 상태를 표시한다.
 • 결과: - 광고주는 비용 발생 여부와 성과 근거를 확인하고 예산·상품 조정 판단을 할 수 있다.
 • dashboardviewed, conversionevidenceviewed, performancealert_shown 이벤트를 기록한다.
 • 예외: - 집계가 지연되면 마지막 갱신 시각과 잠정 집계 상태를 표시한다.
 • 전환 0건 기간에는 과금액 0원과 노출·클릭을 함께 표시한다.
 • 권한 없는 캠페인 식별자 조회는 데이터를 반환하지 않고 접근 거부를 기록한다.
 • 환불 차감이 발생하면 이전 확정 비용과 조정 금액을 분리 표시한다.
-• 표시: - 상단 요약에는 노출, 클릭, 광고 기여 전환, 전환율, 전환당 비용, 누적 비용, 잔여 예산을 표시한다.
-• 전환 상태별 표와 과금 근거 상세 화면을 제공한다.
-• 제한·예산 소진·급격한 성과 변화에는 원인과 권장 조치를 안내한다.
+• 표시: - 광고주 화면은 과금 전환과 순증분 전환을 별도 카드로 표시하고 각 측정 목적을 설명한다.
+• 운영자 화면은 holdout 표본 충족·신뢰도·오가닉 추천 잠식률·광고 밀도·점유율을 표시한다.
+• holdout 결과가 지연되거나 표본이 부족하면 잠정 상태와 정산 보정 미적용 사실을 표시한다.
 • 권한 &amp; 접근: - 광고주는 자기 사업자 캠페인만 조회하고 다운로드할 수 있다.
 • 광고 운영자는 담당 범위의 캠페인을 조회할 수 있다.
 • 비즈니스 규칙: - 비용 지표는 확정 전환과 잠정 전환을 구분해 표시한다.
 • 0원 과금은 노출·클릭만 발생했고 유효 전환이 확정되지 않은 상태를 뜻한다.
 • 다운로드에는 권한 범위의 필터 결과만 포함한다.
-• 데이터: - 대시보드 집계는 campaignId, 기준일, 지면Id, 상품Id, 전환유형, 노출수, 클릭수, 잠정전환수, 확정전환수, 무효전환수, 비용, 잔여예산을 가진다.
-• 전환 근거 조회는 전환 식별자, 상태, 발생시각, 적용 단가, 조정 사유를 가진다.</t>
+• 데이터: - 증분성 집계는 campaignId, placementKey, holdoutExperimentId, 기준일, 노출군전환수, 대조군전환수, 순증분전환수, 증분전환율, 신뢰도, 표본충족여부, 오가닉추천잠식률, 신규고객도달수, 신규고객획득수, 정산보정상태를 가진다.
+• 광고 밀도 집계는 placementKey, 기준일, 추천카드수, 광고카드수, 광고밀도, 광고점유율을 가진다.</t>
   </si>
   <si>
     <t>5 플랫폼 운영·정산·보장 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">성과형 상품의 참여 자격, 전환 검증, 정산, 캠페인 한도, 파일럿 게이트와 확대·축소 조건을 운영할 수 있는 관리자 기능을 제공한다. MVP의 보장은 고정 전환 건수 보장이 아니라 유효 전환 발생분에 대해서만 과금하는 순수 성과형 정책으로 정의한다.
-1. ○ Given 관리자가 파일럿 운영 권한을 보유할 때, When 카테고리·지면·셀러 등급·상품 품질·예산 및 노출 한도를 설정하면, Then 변경 값과 변경자를 감사 로그에 저장한다.
-2. ○ Given 잠정 전환이 검증 대기 상태일 때, When 관리자가 증빙과 이상 탐지 결과를 검토하면, Then 승인·무효·보류 상태 중 하나로 처리하고 정산 대상 여부를 갱신한다.
-3. ○ Given 공짜 소진율·전환율·예측 오차·마진이 파일럿 게이트를 벗어났을 때, When 가드레일 평가가 실행되면, Then 해당 카테고리·지면 또는 캠페인의 노출 한도를 축소하거나 신규 유입을 중단한다.
-4. ○ Given 대형 브랜드의 CPD 캠페인이 존재할 때, When 성과형 상품광고 운영 정책을 적용하면, Then CPD 캠페인은 성과형 캠페인으로 자동 전환되지 않고 별도 매출로 집계된다.</t>
+    <t xml:space="preserve">관리자가 홈 개인화 추천 피드의 sponsored 슬롯, 광고 밀도 캡, 추천 적합도 기준, holdout 실험, 전환 검증과 정산 보정을 운영할 수 있게 한다. 신규 성과형과 기존 oCPM의 동일 경매 구조 및 기존 지면 매출 유지율을 관리한다. 고정 전환 건수 보장은 포함하지 않으며, 유효 전환 발생분만 과금하는 순수 성과형 원칙을 유지한다.
+1. ○ Given 관리자가 파일럿 운영 권한을 보유할 때, When 홈 추천 피드 sponsored 슬롯·추천 N개당 광고 1개 밀도 캡·셀러 등급·예산·노출 한도를 설정하면, Then 변경 값과 변경자를 감사 로그에 저장한다.
+2. ○ Given holdout 실험이 실행 중일 때, When 관리자가 실험군·대조군·표본 충족·결과 지연을 검토하면, Then 실험 상태와 정산 보정 적용 여부를 기록한다.
+3. ○ Given 공짜 소진율·증분 전환율·오가닉 추천 잠식률·광고 점유율·지면 매출 유지율이 파일럿 기준을 벗어났을 때, When 가드레일 평가가 실행되면, Then 성과형 노출 한도를 축소하거나 신규 유입을 중단한다.
+4. ○ Given 대형 브랜드의 CPD 또는 기존 oCPM 캠페인이 존재할 때, When 성과형 상품광고 운영 정책을 적용하면, Then 기존 캠페인은 자동 전환하지 않고 같은 sponsored 슬롯 경매에서 별도 과금 방식으로 집계한다.</t>
   </si>
   <si>
     <t>5.1 파일럿 운영·검증·정산 콘솔</t>
   </si>
   <si>
-    <t xml:space="preserve">관리자가 참여 자격, 전환 검증, 정산 조정 및 수익성 가드레일을 운영하는 기능이다. 성과형 캠페인의 제한·중단과 청구 대상 확정을 관리하되 대형 브랜드 CPD는 별도 상품으로 유지한다.
+    <t xml:space="preserve">관리자가 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 참여 자격, 추천 적합도·밀도 캡, holdout 실험, 전환 검증, 증분성 정산 보정 및 수익 가드레일을 운영하는 기능이다. 신규 성과형과 기존 oCPM의 동일 경매·별도 과금 방식을 함께 관리한다. 대형 브랜드 CPD는 별도 상품으로 유지한다.
 [기능의 근거] 순수 성과형 과금의 신뢰성과 기존 지면 수익 방어를 동시에 운영해야 한다.
 [성공 기준] 지면 매출 유지율을 기존 oCPM 대비 95% 이상으로 유지한다.
 [개발 준비 슬롯]
@@ -404,12 +435,9 @@
 • 트리거: - 관리자가 참여 자격·한도·전환 검증·정산 메뉴를 선택한다.
 • 일일 가드레일 평가 또는 월간 청구서 생성 작업이 실행된다.
 • 광고주 이의 제기 또는 이상 탐지 경보가 접수된다.
-• 동작: - 관리자가 카테고리·지면·셀러 등급·상품 품질·예산·노출 한도와 졸업 셀러의 성과형 월 집행 상한을 설정한다.
-• 관리자가 최근 유상 광고 집행 이력, 품질 게이트, 누적 유효 전환 수를 확인해 신규·졸업 대기·졸업 상태를 검토한다.
-• 관리자가 잠정 전환의 주문·마지막 유효 클릭·전환 로그와 이상 탐지 결과를 검토해 승인·무효·보류 처리한다.
-• 플랫폼이 확정 전환 비용을 월간 청구서에 반영하고 환불·이의 조정액을 다음 달 청구서 또는 광고 크레딧으로 반영한다.
-• 플랫폼이 공짜 소진율과 별도로 카테고리 평균 주문금액 및 거래 수수료 기여를 수익 가드 지표로 모니터링한다.
-• FE는 운영 콘솔과 감사 화면을 만들고 BE는 권한·상태·청구 처리를 수행하며 Data·ML은 가드레일·이상 탐지를 제공하고 정산은 청구·조정 확정을 수행한다.
+• 동작: - 관리자가 홈 추천 피드 sponsored 슬롯, 추천 N개당 광고 1개 밀도 캡, 광고 점유율 상한, 추천 적합도 최소 기준을 설정한다.
+• 관리자가 holdout 실험의 대상, 배정, 표본 충족, 결과 지연, 정산 보정 적용 상태를 검토한다.
+• 관리자가 last-click 과금 전환과 holdout 증분성 결과를 분리해 정산 보정 여부를 승인·보류한다.
 • 결과: - 운영 설정, 전환 판정, 제한 조치, 청구서 및 조정 내역을 감사 로그와 함께 저장한다.
 • 가드레일 위반 시 신규 유입 중단 또는 노출 한도 축소를 실행한다.
 • conversionreviewed, guardrailtriggered, invoice_issued 이벤트를 기록한다.
@@ -417,22 +445,18 @@
 • 청구서 발행 후 이의가 접수되면 원 청구 내역을 보존하고 조정 건을 별도 생성한다.
 • 정산 연동 실패 시 청구서 상태를 발행 보류로 두고 재처리한다.
 • 가드레일 산출 데이터가 누락되면 자동 확대를 막고 운영자 검토로 전환한다.
-• 표시: - 콘솔은 신규 광고주 판정, 졸업 대기·졸업 상태, 참여 자격, 전환 검증 대기열, 정산·이의, 가드레일 모니터링을 분리해 표시한다.
-• 콘솔은 졸업 대상의 누적 유효 전환 수, oCPM 전환 안내 상태와 성과형 월 집행 상한을 표시한다.
-• 가드레일 위반은 영향 범위, 기준값, 현재값, 적용 조치를 표시한다.
-• 가드레일 화면은 공짜 소진율과 함께 카테고리 평균 주문금액·거래 수수료 기여를 표시한다.
+• 표시: - 콘솔은 홈 추천 피드 sponsored 슬롯별 광고 밀도·점유율, 기존 oCPM·신규 성과형 경매 결과, 추천 적합도 제한을 표시한다.
+• 콘솔은 holdout 실험군·대조군, 표본 충족, 신뢰도, 순증분 전환, 오가닉 추천 잠식률, 정산 보정 상태를 표시한다.
 • 권한 &amp; 접근: - 플랫폼 관리자는 정책·한도 설정을 변경할 수 있다.
 • 정산·고객지원 담당자는 청구서·이의·조정을 처리할 수 있다.
 • 광고 운영자는 담당 범위에서 자격·전환 검토를 수행할 수 있다.
-• 비즈니스 규칙: - 내부 전환은 D+7, 외부 전환은 D+14에 확정한다.
-• 전환 귀속은 기여 윈도우 안의 마지막 유효 클릭 1건만 인정하고 view-through 기여는 MVP에서 과금하지 않는다.
-• 누적 유효 전환 50건은 성과 검증 완료·oCPM 전환 안내 기준이며, 졸업 후 성과형 월 집행 상한을 적용한다.
-• 공짜 소진율이 20%를 초과하면 신규 성과형 캠페인 유입을 중단하고 기존 노출 한도를 축소한다.
-• 신규 광고주 한정과 졸업 후 성과형 월 집행 상한은 eCPM 동일 경매·oCPM 바닥가 가드레일·지면 매출 유지율과 함께 기존 oCPM 매출 잠식을 막는 1차 장치이다.
+• 비즈니스 규칙: - 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 성과형과 기존 oCPM을 동일 경매로 운영한다.
+• 추천 N개당 광고 1개 이하의 밀도 캡과 광고 라벨을 유지한다.
+• holdout 결과는 수익 검증·정산 보정용이며 last-click 과금 귀속을 대체하지 않는다.
+• 표본 충족 또는 신뢰도 기준을 넘지 못한 holdout 결과는 정산 보정과 자동 확대에 사용하지 않는다.
 • CPD는 성과형 상품으로 자동 전환하지 않는다.
-• 데이터: - 정산 내역은 settlementId, campaignId, billingMonth, 확정전환수, 청구금액, 조정금액, 상태, 청구서Id를 가진다.
-• 가드레일 결과는 평가일, 카테고리, 지면, 신규광고주비중, 졸업셀러성과형집행액, 공짜소진율, 매출유지율, 예측오차, 평균주문금액, 거래수수료기여, 수익가드판정, 조치상태를 가진다.
-• 감사 로그는 actorId, 역할, 대상유형, 대상Id, 이전값, 변경값, 변경시각을 가진다.</t>
+• 데이터: - 가드레일 결과는 placementKey, 광고밀도, 광고점유율, 추천적합도미달률, 증분전환율, 오가닉추천잠식률, holdout표본충족여부, holdout결과지연, 정산보정상태를 추가로 가진다.
+• holdout 운영 기록은 experimentId, 대상범위, 배정방식, 시작·종료일, 표본목표, 현재표본, 신뢰도, 상태, 결과버전을 가진다.</t>
   </si>
   <si>
     <t>플랫폼 관리자, 광고 운영자, 정산·고객지원 담당자, 데이터·분석 담당자</t>
@@ -441,11 +465,11 @@
     <t>6 단계적 출시 및 확장 로드맵</t>
   </si>
   <si>
-    <t xml:space="preserve">1단계는 에이블리 입점 중소·신규 셀러와 전환이 활발한 패션·뷰티 카테고리, 기존 활성 지면을 대상으로 제한된 파일럿을 운영한다. 2단계는 공짜 소진율·마진·예측 정확도·재집행률이 기준을 통과하면 대상 카테고리와 셀러를 확대한다. 3단계에서 외부 미입점 광고주, 추가 지면, CPA 상한 및 전환 건수 보장을 검토한다.
-1. ○ Given 파일럿 출시를 준비할 때, When 대상 카테고리·지면·셀러 수·기간과 사전 핵심 지표 임계값을 등록하면, Then 승인 전에는 집행을 시작할 수 없다.
-2. ○ Given 파일럿 평가 기간이 종료되었을 때, When 성장·수익성·건전성 지표를 산출하면, Then 확대·유지·축소·중단 중 하나의 결정을 기록한다.
-3. ○ Given 공짜 소진율이 20%를 초과하거나 지면 매출 유지율이 90% 미만으로 지속될 때, When 축소·중단 규칙이 평가되면, Then 신규 성과형 캠페인 유입을 중단하거나 기존 노출 한도를 축소한다.
-4. ○ Given Phase 2에서 소액 기존 중소 셀러 확대를 검토할 때, When 운영 데이터와 머신러닝 학습 안정성을 평가하면, Then 졸업 기준 상향과 eCPM 경매·집행 상한 방어안을 MVP와 분리해 기록한다.</t>
+    <t xml:space="preserve">홈 개인화 추천 피드의 기존 sponsored 슬롯에서 제한된 신규 광고주 성과형 파일럿을 운영하고, 증분성·오가닉 보호·지면 수익을 함께 검증한 뒤 확대 여부를 결정한다. MVP는 기존 슬롯의 과금 옵션 추가 범위로 한정한다. 추가 지면, 외부 미입점 광고주, 목표 CPA 입찰과 CPA 보장은 Phase 2 이후 후보로 관리한다.
+1. ○ Given 파일럿 출시를 준비할 때, When 홈 개인화 추천 피드 sponsored 슬롯·광고 밀도 캡·holdout 설계·대상 셀러 수·기간·핵심 지표 임계값을 등록하면, Then 승인 전에는 집행을 시작할 수 없다.
+2. ○ Given 파일럿 평가 기간이 종료되었을 때, When 성장·수익성·증분성·오가닉 보호·건전성 지표를 산출하면, Then 확대·유지·축소·중단 중 하나의 결정을 기록한다.
+3. ○ Given 공짜 소진율이 20%를 초과하거나 지면 매출 유지율이 90% 미만이거나 오가닉 추천 잠식률이 목표를 초과할 때, When 축소·중단 규칙이 평가되면, Then 신규 성과형 캠페인 유입을 중단하거나 추천 피드 점유율을 축소한다.
+4. ○ Given Phase 2에서 소액 기존 중소 셀러 또는 추가 발견 지면 확대를 검토할 때, When 운영 데이터·추천 모델 안정성·holdout 결과를 평가하면, Then 졸업 기준 상향과 eCPM 경매·밀도 캡·집행 상한 방어안을 MVP와 분리해 기록한다.</t>
   </si>
   <si>
     <t>중간</t>
@@ -454,7 +478,7 @@
     <t>6.1 파일럿 게이트와 단계적 확대 관리</t>
   </si>
   <si>
-    <t xml:space="preserve">파일럿 대상·기간·핵심 지표 게이트를 등록하고 결과에 따라 확대·유지·축소·중단을 결정하는 기능이다. MVP는 유상 광고 집행 이력이 없는 신규 광고주로 대상을 한정하고, 누적 유효 전환 50건의 졸업 트리거와 성과형 월 집행 상한으로 기존 oCPM 매출 잠식을 방어한다. 외부 미입점 광고주, 목표 CPA 입찰, CPA 상한 및 전환 건수 보장은 Phase 2 후보로 별도 관리한다.
+    <t xml:space="preserve">홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 광고주 성과형 파일럿을 운영하고, 증분성·오가닉 보호·지면 수익을 기준으로 확대·유지·축소·중단을 결정하는 기능이다. MVP는 기존 슬롯의 과금 옵션 추가로 한정한다. 추가 발견 지면과 외부 미입점 광고주, 목표 CPA 입찰은 holdout 검증 후 Phase 2 후보로 관리한다.
 [기능의 근거] 제한된 파일럿에서 수익성과 건전성을 검증한 뒤 안전하게 대상 카테고리와 셀러를 확대해야 한다.
 [성공 기준] 신규 성과형 광고주 수 300명과 성과형 광고 매출 비중 5% 이상을 달성한다.
 [개발 준비 슬롯]
@@ -463,11 +487,9 @@
 • 트리거: - 관리자가 파일럿 계획을 등록하거나 승인한다.
 • 일일 모니터링 또는 파일럿 종료 평가가 실행된다.
 • 확대·축소·중단 임계값을 충족한다.
-• 동작: - 관리자가 패션·뷰티, 전환이 활발한 기존 지면, 초기 대상 셀러를 등록한다.
-• 플랫폼이 성장·수익성·건전성 지표와 신규 한정·집행 상한의 매출 잠식 방어 효과를 파일럿·확대·축소 기준과 비교한다.
-• 플랫폼이 확대·유지·축소·중단 결정을 기록하고 대상·노출 한도에 반영한다.
-• Phase 2에서 소액 기존 중소 셀러 확대를 검토할 때 플랫폼은 내부 머신러닝 학습 안정성과 운영 데이터를 바탕으로 졸업 기준 상향안을 평가한다.
-• FE는 게이트 설정과 결과 화면을 만들고 BE는 승인·결정 상태를 처리하며 Data·ML은 지표 산출을 제공하고 정산은 총 기여 산정 데이터를 제공한다.
+• 동작: - 관리자가 홈 개인화 추천 피드 sponsored 슬롯, 추천 N개당 광고 1개 밀도 캡, holdout 설계, 초기 대상 셀러를 등록한다.
+• 플랫폼이 성장·수익성·증분성·오가닉 추천 잠식·광고 밀도·지면 매출 유지율을 파일럿 게이트와 비교한다.
+• 플랫폼이 표본 충족과 holdout 결과 신뢰도를 확인한 뒤 확대·유지·축소·중단 결정을 기록한다.
 • 결과: - 파일럿 계획, 승인, 지표 스냅샷, 의사결정 및 후속 조치를 저장한다.
 • 확대 결정 시 대상 카테고리·지면·셀러 범위를 늘리고 축소·중단 시 한도를 줄인다.
 • pilotapproved, pilotevaluated, rollout_decided 이벤트를 기록한다.
@@ -479,15 +501,12 @@
 • 축소·중단 경보에는 영향 카테고리·지면과 실행된 제한 조치를 표시한다.
 • 권한 &amp; 접근: - 플랫폼 관리자만 파일럿 승인과 확대·축소·중단 결정을 확정할 수 있다.
 • 광고 운영자와 데이터·분석 담당자는 결과를 조회하고 근거를 제출할 수 있다.
-• 비즈니스 규칙: - 파일럿은 패션·뷰티와 기존 활성 상품광고 지면을 우선 대상으로 한다.
-• 초기 파일럿은 카테고리별 20~30개, 총 100개 레퍼런스 셀러를 목표로 한다.
-• MVP 참여 대상은 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주이며, 기존 품질 게이트를 유지한다.
-• 확대 게이트는 신규 광고주 500명 이상, 전환 발생률 40% 이상, 재집행률 35% 이상, 성과형 광고 매출 비중 10% 이상이다.
-• Phase 2에서 소액 기존 중소 셀러로 확대할 때는 졸업 기준 50건 상향을 검토하고, eCPM 동일 경매와 성과형 월 집행 상한으로 기존 oCPM 매출 잠식을 방어한다.
-• 외부 미입점 광고주, 목표 CPA 입찰, CPA 상한 보장, 전환 건수 보장은 Phase 2 후보이다.
-• 데이터: - 파일럿 계획은 pilotId, 대상카테고리, 대상지면, 대상셀러수, 시작·종료일, 승인상태, 게이트버전을 가진다.
-• 지표 스냅샷은 pilotId, 기준일, 신규광고주수, 전환발생률, 재집행률, 매출비중, 매출유지율, 공짜소진율, 예측오차, 졸업셀러수, oCPM전환안내율, 결정값을 가진다.
-• Phase 2 후보는 후보Id, 이름, 범위, 보류사유, 재검토조건, 상태를 가진다.</t>
+• 비즈니스 규칙: - MVP 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 sponsored 슬롯이다.
+• MVP는 신규 지면 개발이 아니라 기존 슬롯의 신규 광고주 한정 전환 성과형 과금 옵션이다.
+• 추천 N개당 광고 1개 이하의 밀도 캡과 지면 매출 유지율 95% 이상을 유지한다.
+• Phase 2의 추가 발견 지면·소액 기존 중소 셀러 확대는 holdout 증분성·오가닉 보호·추천 모델 안정성 결과를 충족한 뒤 검토한다.
+• 데이터: - 파일럿 계획은 placementKey, 광고밀도캡, 광고점유율상한, holdoutExperimentId, 오가닉잠식목표를 추가로 가진다.
+• 지표 스냅샷은 증분전환율, 오가닉추천잠식률, 신규고객도달수, 신규고객획득수, 광고밀도, 광고점유율, holdout표본충족여부, holdout신뢰도를 추가로 가진다.</t>
   </si>
   <si>
     <t>플랫폼 관리자, 광고 운영자, 데이터·분석 담당자</t>
@@ -532,13 +551,19 @@
     <t>상품광고 경매 및 노출 배분 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">MVP·Phase 2 노출 경쟁 구조: - MVP에서 광고주는 전환 단가를 입찰하지 않고 플랫폼이 카테고리 기준단가를 제시한다.
-- MVP의 전환 단가는 지면·상품·셀러의 품질 점수와 예상 전환율을 반영해 카테고리 기준단가의 80~120% 범위에서 조정한다.
-- MVP의 경매 eCPM은 예상 전환율×플랫폼 제시 전환 단가×1,000으로 계산한다.
-- MVP에서 노출 경쟁의 주 변수는 상품·셀러 품질과 사용자 맥락에 따라 달라지는 예상 전환율이며, 전환 단가는 광고주가 직접 경쟁시키는 값이 아니다.
-- Phase 2에서 목표 CPA 입찰을 도입하면 광고주는 희망 전환 단가를 입찰한다.
-- Phase 2의 경매 eCPM은 예상 전환율×광고주 입찰 전환 단가×1,000으로 계산한다.
-- Phase 2에서는 광고주 입찰 전환 단가가 eCPM을 통해 노출 경쟁의 직접 변수로 작동하며, 예상 전환율과 함께 랭킹에 반영한다.</t>
+    <t xml:space="preserve">MVP·Phase 2 노출 경쟁 구조: - MVP 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯이다.
+- MVP는 신규 지면 개발이 아니라 기존 sponsored 슬롯에 신규 광고주 한정 전환 성과형 과금 옵션을 추가한다.
+- 신규 성과형과 기존 oCPM은 같은 sponsored 슬롯에서 동일 경매로 경쟁한다.
+- MVP에서 광고주는 전환 단가를 입찰하지 않고 플랫폼이 카테고리 기준단가를 제시한다.
+- MVP의 신규 성과형 eCPM은 추천 AI 예상 전환율×플랫폼 제시 전환 단가×1,000으로 계산한다.
+- 랭킹은 eCPM, 추천 적합도, 상품·셀러 품질 점수를 함께 반영한다.
+- Phase 2 목표 CPA 입찰에서는 광고주 입찰 전환 단가가 eCPM의 직접 변수로 추가된다.
+추천 슬롯 보호 규칙: - 광고 노출 상품은 오가닉 추천 상품 카드와 동일한 네이티브 UI를 사용하고 광고 라벨을 유지한다.
+- 홈 개인화 추천 피드는 추천 N개당 광고 1개 이하의 밀도 캡을 적용한다.
+- 예상 eCPM, 추천 적합도 또는 품질 점수 중 하나가 최소 기준에 미달하면 해당 광고를 노출하지 않는다.
+- 예상 eCPM이 oCPM 바닥가의 95% 미만이면 성과형 광고 우선순위를 낮춘다.
+- 예상 eCPM이 oCPM 바닥가의 80% 미만이면 성과형 광고 대신 기존 oCPM 캠페인을 노출한다.
+홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 성과형과 기존 oCPM의 동일 경매·노출 배분을 정한다.</t>
   </si>
   <si>
     <t>PL-BMLDRR</t>
@@ -549,20 +574,21 @@
   <si>
     <t xml:space="preserve">검증·정산 주기: - 내부 구매·쿠폰 사용 전환은 발생일 기준으로 잠정 집계하고 D+7에 유효 여부를 확정한다.
 - 외부 전환은 광고주 포스트백 또는 전환 API 수신 후 잠정 집계하고 D+14에 유효 여부를 확정한다.
-- 확정 전환 비용은 매일 누적 표시하고, 광고주 청구서는 매월 1일~말일 확정분을 기준으로 다음 달 5일 발행한다.
+- holdout 증분성 결과는 전환 확정 데이터가 집계된 뒤 산출하며, 표본과 신뢰도 기준 충족 시에만 정산 보정 후보로 사용한다.
+- 확정 전환 비용은 매일 누적 표시하고 광고주 청구서는 매월 1일~말일 확정분을 기준으로 다음 달 5일 발행한다.
 - 광고주는 청구서 발행 후 7일 이내에 이의를 제기할 수 있다.
-유효 전환 기준: - MVP의 유효 전환 유형은 구매와 쿠폰 사용이며 앱 설치 전환은 해당 캠페인에 한해 별도 승인 후 적용하거나 Phase 2에서 도입한다.
-- 구매 전환은 광고 기여 윈도우 안에 발생한 결제 완료 주문만 유효 전환으로 인정한다.
-- 쿠폰 사용 전환은 광고 기여 윈도우 안에 발생한 유효 쿠폰 사용만 유효 전환으로 인정한다.
-- 전환 귀속은 기여 윈도우 안의 마지막 유효 클릭 1건만 인정하며, 한 전환에 복수 광고 클릭이 있으면 가장 늦은 유효 클릭의 캠페인에만 귀속한다.
+유효 전환 및 증분성 기준: - MVP의 유효 전환 유형은 구매와 쿠폰 사용이며 앱 설치 전환은 Phase 2 후보이다.
+- 과금 전환 귀속은 클릭 후 7일 기여 윈도우 안의 마지막 유효 클릭 1건만 인정한다.
 - 노출만 발생한 view-through 기여는 MVP의 과금·정산 대상에서 제외한다.
-- 동일 주문·동일 쿠폰 사용 이벤트는 한 번만 과금한다.
+- 동일 주문·동일 쿠폰 사용 이벤트는 멱등키로 한 번만 과금한다.
 - 취소·환불·부정 거래·셀프 구매·정책 위반 전환은 과금 대상에서 제외한다.
-- 광고 기여 윈도우 일수는 캠페인 유형별로 설정하고 파일럿 기본값은 클릭 후 7일로 둔다.
-분쟁·환불 조정: - 이상 패턴이 탐지된 전환 비용은 검증 완료 전까지 정산 보류 상태로 표시한다.
-- 광고주 이의 제기는 주문·마지막 유효 클릭·전환 로그와 어뷰징 판정 결과를 기준으로 검토한다.
+- holdout은 홈 추천 피드 광고가 없었어도 오가닉 추천으로 발생했을 전환을 제외한 순증분 전환 측정용이며, last-click 과금 귀속을 대체하지 않는다.
+- holdout 결과는 수익 검증·정산 보정용으로 사용하고 표본·신뢰도 미달 또는 지연 시 기존 과금 확정 규칙을 유지한다.
+분쟁·환불·증분성 보정: - 이상 패턴이 탐지된 전환 비용은 검증 완료 전까지 정산 보류 상태로 표시한다.
 - 확정 후 취소·환불이 발생한 전환 비용은 다음 달 청구서에서 차감한다.
-- 이미 납부한 비용의 조정액은 다음 달 광고 크레딧으로 우선 반영한다.</t>
+- holdout 결과가 표본·신뢰도 기준을 충족해 보정이 승인되면 정산 보정 내역에 실험 버전·대상 기간·보정 근거를 기록한다.
+- holdout 결과가 재산출되거나 오염이 확인되면 이미 발행된 청구 내역은 보존하고 별도 조정 건으로 처리한다.
+last-click 과금 귀속과 holdout 증분 검증·정산 보정의 역할을 분리해 전환 확정·정산을 정한다.</t>
   </si>
   <si>
     <t>PL-PVAXPM</t>
@@ -571,23 +597,24 @@
     <t>성과형 상품광고 GTM 및 온보딩 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">파일럿 대상: - 파일럿은 패션·뷰티 카테고리와 전환이 활발한 기존 상품광고 지면을 우선 대상으로 한다.
-- MVP 대상은 최근 N개월 유상 광고 집행 이력이 0원인 입점 신규 광고주이며, 에이블리 기존 신규 광고주·무상 광고비 판정과 같은 내부 광고 집행 이력으로 판단한다.
-- 별도 매출·거래액 증빙 서류는 요구하지 않는다.
-- 초기 초대 대상은 최근 90일 주문 30건 이상, 상품 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 기준을 충족한 셀러로 선정한다.
-- 배송 지연·취소율과 정책 위반 이력이 내부 기준을 초과한 셀러는 파일럿 대상에서 제외한다.
+    <t xml:space="preserve">파일럿 대상·지면: - 파일럿 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯이다.
+- MVP는 신규 지면이 아니라 기존 sponsored 슬롯의 신규 광고주 한정 전환 성과형 과금 옵션이다.
+- MVP 대상은 최근 N개월 유상 광고 집행 이력이 0원인 입점 신규 광고주이며 별도 매출·거래액 증빙 서류는 요구하지 않는다.
+- 초기 초대 대상은 최근 90일 주문 30건 이상, 상품 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 기준을 충족한 셀러다.
+- 추천 N개당 광고 1개 이하의 밀도 캡을 유지한다.
 - 카테고리별 20~30개, 총 100개 레퍼런스 셀러를 1차 모집 목표로 둔다.
-세일즈 메시지: - 초대 메시지는 ‘성과 없으면 0원, 구매·쿠폰 사용 전환 발생분만 과금’을 핵심 문구로 사용한다.
-- 초대 메시지는 권장 상품, 예상 전환 수, 예상 비용 범위와 기존 상품광고 지면 정보를 함께 제공한다.
+세일즈 메시지: - 초대 메시지는 ‘홈 추천 피드에서 성과 없으면 0원, 구매·쿠폰 사용 유효 전환 발생분만 과금’을 핵심 문구로 사용한다.
+- 초대 메시지는 추천 상품 카드와 동일한 네이티브 UI 및 광고 라벨을 유지하는 기존 sponsored 슬롯 상품임을 안내한다.
+- BD 담당자는 브랜드를 모르는 신규 고객에게 발견 지면에서 도달하고, 신규 고객 획득 성과에만 비용을 내는 상품으로 제안한다.
+- 광고주에게는 last-click 과금 전환과 holdout 기반 순증분 성과를 구분해 안내한다.
 - 누적 유효 전환 50건에 근접한 셀러에게는 성과 검증 완료 예정과 oCPM 유상 광고 전환 안내를 제공한다.
-- BD 담당자는 첫 캠페인 성과가 확인된 셀러의 전환율·광고 기여 매출 사례를 익명화해 같은 카테고리 셀러에게 제시한다.
-온보딩·졸업 흐름: - 셀러는 초대 메시지에서 셀러센터의 성과형 상품광고 소개 화면으로 진입한다.
-- 셀러는 대상 상품을 선택하고 권장 전환 단가·일일 예산·예상 비용을 확인한다.
-- 셀러는 전환 과금·검증·환불 조정 기준에 동의한 후 캠페인을 시작한다.
+온보딩·졸업 흐름: - 셀러는 초대 메시지에서 홈 추천 피드 성과형 상품광고 소개 화면으로 진입한다.
+- 셀러는 대상 상품을 선택하고 추천 AI 예측 기반 권장 전환 단가·일일 예산·예상 비용을 확인한다.
+- 셀러는 전환 과금·검증·환불 조정 및 증분성 측정 기준에 동의한 후 캠페인을 시작한다.
 - 셀러 상태는 신규-성과형에서 누적 유효 전환 50건 근접 시 졸업 대기로 전이한다.
 - 셀러 상태는 누적 유효 전환 50건 달성 시 졸업으로 전이하고 oCPM 유상 광고 전환을 안내한다.
 - 졸업 셀러는 성과형 월 집행 상한 안에서 성과형 캠페인을 계속 사용할 수 있다.
-- BD 또는 셀러센터는 시작 후 7일에 성과 리포트와 예산·상품 조정 제안을 제공한다.</t>
+홈 개인화 추천 피드 기존 sponsored 슬롯의 신규 광고주 성과형 파일럿 대상과 세일즈 메시지를 정한다.</t>
   </si>
   <si>
     <t>PL-BDBECW</t>
@@ -597,36 +624,47 @@
   </si>
   <si>
     <t xml:space="preserve">[공통 정의]
-용어 정의: - 유효 전환은 기여 윈도우 안에 발생하고 마지막 유효 클릭 기준 귀속, 중복·취소·환불·부정 거래·정책 위반 검증을 통과해 과금 가능한 구매 또는 쿠폰 사용 전환이다.
-- 마지막 유효 클릭은 전환 발생 전 기여 윈도우 안에 있는 광고 클릭 중 가장 늦은 유효 클릭이며, 한 전환은 해당 클릭 1건에만 귀속한다.
-- view-through 기여는 광고 노출만으로 전환을 귀속하는 방식이며 MVP의 측정·과금·정산에서 제외한다.
-- 공짜 소진율은 성과형 캠페인에 배정된 노출 중 유효 전환 비용이 발생하지 않은 노출의 비율이다.
-- eCPM은 예상 전환율×전환 단가×1,000으로 계산하는 경매 비교값이다.
-- 기여 윈도우는 광고 클릭 후 전환을 광고 기여로 인정하는 기간이며 파일럿 기본값은 7일이다.
-- 증분성은 자연전환과 기존 oCPM 베이스라인을 제외한 신규 셀러의 광고 기여 증분 GMV와 수수료 기여를 뜻한다.
-데이터 모델: - 캠페인은 campaignId, sellerId, 상품Id, 전환유형, 상태, 기간, 예산, 적용전환단가, 누적비용, 잔여예산, 상품가구간, 수익가드판정을 저장한다.
-- 전환 이벤트는 conversionId, idempotencyKey, campaignId, 원이벤트Id, 발생·수신시각, 마지막유효클릭Id, 검증상태, 무효사유, 적용단가를 저장한다.
-- 정산 내역은 settlementId, campaignId, 청구월, 확정전환수, 청구금액, 조정금액, 상태, 청구서Id를 저장한다.
-- 셀러 참여 자격은 sellerId, 평가일, 주문수, 평점, 품절률, 배송품질, 평균주문금액, 예상수수료기여, 수익가드판정, 적격여부, 제한사유를 저장한다.
-상태 머신: - 캠페인은 초안에서 심사로 전이하고 심사 승인 후 집행중으로 전이한다.
-- 캠페인은 예산·품질·수익 가드·가드레일 위반 시 제한으로 전이하며, 운영자 또는 정책 판단으로 중단으로 전이한다.
-- 전환은 잠정 집계에서 내부 전환 D+7 또는 외부 전환 D+14 검증을 거쳐 확정으로 전이한다.
-- 전환은 검증 실패 시 무효로 전이하고 확정 후 취소·환불 시 환불 차감으로 전이한다.
+용어 정의: - 기존 sponsored 슬롯은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’ 안에서 기존 oCPM 광고가 노출되는 광고 슬롯이다.
+- 신규 성과형은 신규 광고주에게 유효 전환 시에만 비용을 청구하는 기존 sponsored 슬롯의 과금 옵션이다.
+- eCPM은 추천 AI 예상 전환율×전환 단가×1,000으로 계산하는 신규 성과형의 경매 비교값이다.
+- last-click은 클릭 후 7일 기여 윈도우 안의 가장 늦은 유효 클릭이며 과금 귀속용이다.
+- holdout 증분성은 노출군과 광고 미노출 유사 대조군의 전환 차이로 오가닉 추천을 제외한 순증분 전환을 산정하는 방식이다.
+- view-through 기여는 광고 노출만으로 전환을 귀속하는 방식이며 MVP의 과금·정산 대상에서 제외한다.
+데이터 모델: - 캠페인은 campaignId, sellerId, 상품Id, placementKey, billingModel, 상태, 예산, 적용전환단가, 누적비용, 누적유효전환수, 성과형월집행상한을 저장한다.
+- 경매 후보는 requestId, placementKey, campaignId, billingModel, 예상전환율, 추천적합도, 품질점수, eCPM, oCPM바닥가, 밀도캡판정, 노출결과, 미노출사유, 모델버전을 저장한다.
+- 전환 이벤트는 conversionId, idempotencyKey, campaignId, 광고노출Id, holdoutExperimentId, holdoutCohort, 마지막유효클릭Id, 검증상태, 정산보정상태를 저장한다.
+- holdout 실험은 experimentId, placementKey, campaignId, 배정규칙버전, 노출군비율, 대조군비율, 시작·종료일, 상태, 결과버전을 저장한다.
+- 증분성 결과는 experimentId, 노출군·대조군 표본과 전환수, 순증분전환수, 증분전환율, 신뢰도, 오염률, 표본충족여부, 정산보정상태를 저장한다.
+상태 머신: - 캠페인은 초안에서 심사, 집행중, 제한, 중단으로 전이하며 누적 유효 전환 50건 근접 시 졸업 대기, 달성 시 졸업으로 전이한다.
+- 전환은 잠정 집계에서 내부 D+7 또는 외부 D+14 검증 후 확정으로 전이하고 실패 시 무효, 확정 후 취소·환불 시 환불 차감으로 전이한다.
+- holdout 실험은 설계, 승인, 배정중, 측정중, 결과 산출중, 적격, 미달, 종료 상태로 전이한다.
+- holdout 결과는 표본·신뢰도 충족 시에만 정산 보정 후보로 전이한다.
 [지표·연동]
-지표 산식: - eCPM은 예상전환율×전환단가×1,000으로 계산한다.
-- 유효 전환율은 유효 전환 수÷성과형 광고 노출 수×100으로 계산한다.
-- 공짜 소진율은 유효 전환 비용이 발생하지 않은 성과형 광고 노출 수÷성과형 광고 노출 수×100으로 계산한다.
+지표 산식: - 유효 전환율은 유효 전환 수÷성과형 광고 노출 수×100으로 계산한다.
+- 증분 전환율은 노출군 전환율-미노출 대조군 전환율로 계산한다.
+- 순증분 전환 수는 증분 전환율×노출군 표본 수로 계산한다.
+- 오가닉 추천 잠식률은 광고 노출로 인한 오가닉 추천 전환 감소분÷광고 기여 전환 수×100으로 계산한다.
+- 광고 밀도는 광고 카드 수÷추천 카드 수로 계산하고 추천 N개당 광고 1개 이하로 관리한다.
 - 지면 매출 유지율은 성과형과 oCPM을 합산한 실제 지면 매출÷기존 oCPM 베이스라인 지면 매출×100으로 계산한다.
-- 평균 주문금액은 유효 구매 전환의 주문금액 합계÷유효 구매 전환 수로 계산한다.
-- 거래 수수료 기여는 광고 기여 증분 GMV×거래 수수료율로 계산하며 파일럿 수수료율은 7%로 둔다.
-- 총 기여 기준 손익분기 유효 전환율은 기존 oCPM÷((전환단가×(1-공짜소진율)+평균주문금액×거래수수료율)×1,000)으로 계산한다.
-API·연동 명세: Q. 외부 전환 API·포스트백의 재전송 횟수와 지수 백오프 상한을 어떤 파일럿 기준으로 적용할까요?
+- 거래 수수료 기여는 holdout으로 확인된 광고 기여 순증분 GMV×7%로 계산한다.
+API·연동 명세: - 노출 로그는 impressionId, placementKey, campaignId, billingModel, 사용자비식별키, 피드순서, 광고라벨표시여부, holdoutExperimentId, holdoutCohort, occurredAt을 포함한다.
+- 외부 전환 API·포스트백 요청은 idempotencyKey, conversionId, campaignId, eventType, occurredAt, orderOrEventId, value, currency를 포함한다.
+- 외부 전환 API·포스트백 응답은 accepted, conversionId, processingStatus, receivedAt, errorCode를 포함한다.
+- errorCode는 INVALID_CAMPAIGN_ID, ATTRIBUTION_WINDOW_EXPIRED, IDEMPOTENCY_KEY_CONFLICT, MISSING_REQUIRED_FIELD, INVALID_EVENT_TYPE, UNAUTHORIZED, RETRYABLE_SERVER_ERROR를 제공한다.
+- idempotencyKey는 전환 소스와 원이벤트 식별자를 조합한 유일값이며 동일 키의 중복 수신은 최초 처리 결과를 반환한다.
+- 내부 결제·주문·쿠폰 로그는 결제 완료, 취소, 환불, 쿠폰 사용 이벤트와 campaignId 또는 마지막유효클릭Id 연결값을 전환 수집 서비스에 전달한다.
 [화면·품질]
-화면 명세: - 셀러 캠페인 생성 화면은 상품 선택, 전환 유형, 예산·기간 입력, 적용 단가·예상 전환 수·예상 비용 검토, 약관 동의 순서로 제공한다.
-- 셀러 성과 대시보드는 노출, 클릭, 잠정·확정 전환, 전환율, 전환당 비용, 누적 비용, 잔여 예산, 과금 근거, 제한 알림을 제공한다.
-- 관리자 콘솔은 참여 자격, 전환 검증 대기열, 정산·이의 조정, 공짜 소진율·매출 유지율·예측 오차·평균 주문금액·거래 수수료 기여 가드레일을 제공한다.
-- 관리자 콘솔은 설정·검증·정산·가드레일 변경의 감사 이력을 제공한다.
-비기능 요구사항: Q. 외부 전환 수신과 대시보드 반영 SLA를 어떤 파일럿 기준으로 적용할까요?</t>
+화면 명세: - 셀러 생성 화면은 홈 추천 피드 existing sponsored 슬롯, 전환 단가, 예상 성과, 0원 과금 조건을 표시한다.
+- 광고주 대시보드는 last-click 과금 전환과 holdout 순증분 전환, 오가닉 추천 잠식률, 신규 고객 획득을 분리해 제공한다.
+- 관리자 콘솔은 슬롯별 밀도·점유율, 신규 성과형·기존 oCPM 경매 결과, holdout 표본·신뢰도·정산 보정 상태를 제공한다.
+- 광고주 화면에는 사용자 단위 holdout 배정·원본 식별자를 제공하지 않는다.
+비기능 요구사항: - holdout 결과는 전환 확정 데이터가 반영된 뒤 산출하며, 결과 지연 시 자동 확대와 정산 보정을 막는다.
+- holdout 실험은 표본 목표, 오염률, 신뢰도 및 결과 버전을 기록해 재현 가능해야 한다.
+- 대��보드는 이벤트 수신 후 15분 이내 잠정 집계에 반영한다.
+- 외부 전환 API·포스트백의 월간 가용성 목표는 99.9%로 둔다.
+- 정산 대사는 원화 정수 금액 기준 0원 오차를 허용한다.
+- 개인정보·주문 원본·실험 배정은 역할 기반 접근 통제를 적용하고 모든 생성·변경·판정은 감사 로그로 남긴다.
+홈 개인화 추천 피드 기존 sponsored 슬롯의 성과형 광고, holdout 증분성 측정과 기존 전환·정산 연동의 공통 기술 명세다.</t>
   </si>
   <si>
     <t>PL-ZWIDEK</t>
@@ -841,7 +879,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -893,6 +931,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1245,7 +1286,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J41"/>
+  <dimension ref="B2:J42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1316,7 +1357,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" ht="99.00000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1328,7 +1369,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" ht="118.80000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
@@ -1364,7 +1405,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" ht="118.80000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1376,7 +1417,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" ht="99.00000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>18</v>
       </c>
@@ -1388,7 +1429,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" ht="138.60000000000002" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" ht="118.80000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1400,7 +1441,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" ht="732.6" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" ht="673.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -1412,7 +1453,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" ht="257.40000000000003" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" ht="198.00000000000003" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1584,172 +1625,195 @@
       <c r="J33" s="20"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="14"/>
+      <c r="C34" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="9" t="s">
+      <c r="D34" s="14"/>
+      <c r="E34" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="13"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="14"/>
-      <c r="C35" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="F35" s="17" t="s">
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="14"/>
+      <c r="C36" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="14"/>
+      <c r="E36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G36" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H35" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="I35" s="19" t="s">
+      <c r="H36" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I36" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J35" s="20"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="10" t="s">
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G37" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="13"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="14"/>
-      <c r="C37" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="17" t="s">
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="14"/>
+      <c r="C38" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G38" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H38" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I38" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J37" s="20"/>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="10" t="s">
+      <c r="J38" s="20"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G39" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="14"/>
-      <c r="C39" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="17" t="s">
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="14"/>
+      <c r="C40" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="14"/>
+      <c r="E40" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G40" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="I39" s="19" t="s">
+      <c r="H40" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J39" s="20"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="11" t="s">
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="14"/>
-      <c r="C41" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G41" s="18" t="s">
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="14"/>
+      <c r="C42" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="14"/>
+      <c r="E42" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H41" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="I41" s="19" t="s">
+      <c r="H42" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I42" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="J41" s="20"/>
+      <c r="J42" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -1792,81 +1856,81 @@
     <col min="4" max="4" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>77</v>
+    <row r="2" spans="2:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>86</v>
+        <v>89</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/ably/assets/ably-performance-ad-prd.xlsx
+++ b/ably/assets/ably-performance-ad-prd.xlsx
@@ -1,11 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_FD2A2A4101411B29C3776094058C7892D342B4D5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D691D67-F6BA-45E2-A71D-D4CD38459998}"/>
+  <bookViews>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="기능" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="프로덕트 정책" state="visible" r:id="rId5"/>
+    <sheet name="기능" sheetId="1" r:id="rId1"/>
+    <sheet name="프로덕트 정책" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -20,9 +24,6 @@
     <t>프로젝트 이름</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>프로젝트 관리자</t>
   </si>
   <si>
@@ -83,7 +84,7 @@
     <t>핵심 지표</t>
   </si>
   <si>
-    <t xml:space="preserve">모든 수치와 임계값은 홈 개인화 추천 피드 sponsored 슬롯 파일럿 가정이며 운영 데이터로 보정한다.
+    <t>모든 수치와 임계값은 홈 개인화 추천 피드 sponsored 슬롯 파일럿 가정이며 운영 데이터로 보정한다.
 구분  지표  파일럿 목표  확대 게이트  축소·중단 기준성장  신규 성과형 광고주 수  300명  500명 이상  200명 미만
 성장  첫 캠페인 전환 발생률  35% 이상  40% 이상  25% 미만
 성장  30일 재집행률  30% 이상  35% 이상  20% 미만
@@ -161,7 +162,7 @@
     <t>1 순수 성과형 캠페인 생성 및 과금</t>
   </si>
   <si>
-    <t xml:space="preserve">신규 광고주가 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯에서 순수 성과형 캠페인을 만들고 관리할 수 있게 한다. 이 요구사항은 신규 지면 개발이 아니라 기존 sponsored 슬롯에 전환 과금 옵션을 추가하는 범위이며, 유효 전환 외 노출·클릭에는 비용을 청구하지 않는다. 추천 카드와 동일한 네이티브 UI·광고 라벨·밀도 캡은 포함하고, CPA 상한 보장과 전환 건수 보장은 제외한다.
+    <t>신규 광고주가 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯에서 순수 성과형 캠페인을 만들고 관리할 수 있게 한다. 이 요구사항은 신규 지면 개발이 아니라 기존 sponsored 슬롯에 전환 과금 옵션을 추가하는 범위이며, 유효 전환 외 노출·클릭에는 비용을 청구하지 않는다. 추천 카드와 동일한 네이티브 UI·광고 라벨·밀도 캡은 포함하고, CPA 상한 보장과 전환 건수 보장은 제외한다.
 1. ○ Given 참여 자격을 충족한 신규 입점 셀러가 상품과 전환 유형을 선택했을 때, When 홈 개인화 추천 피드 sponsored 슬롯용 예산과 기간을 입력하면, Then 플랫폼은 적용 전환 단가·예상 전환 수·예상 비용을 표시하고 초안 캠페인을 저장한다.
 2. ○ Given 심사를 통과한 성과형 캠페인이 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 집행 중일 때, When 노출 또는 클릭만 발생하면, Then 캠페인 비용은 0원으로 유지된다.
 3. ○ Given 유효 전환이 확정되었을 때, When 누적 유효 전환 수가 50건에 도달하면, Then 성과 검증 완료로 기록하고 oCPM 유상 광고 전환을 안내하며 성과형 월 집행 상한을 적용한다.
@@ -177,7 +178,7 @@
     <t>1.1 성과형 캠페인 생성 및 비용 관리</t>
   </si>
   <si>
-    <t xml:space="preserve">최근 N개월 유상 광고 집행 이력이 없는 입점 셀러가 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯을 대상으로 순수 성과형 캠페인을 만들고 예산·기간·전환 유형을 관리하는 기능이다. 신규 지면을 만들지 않고 기존 sponsored 슬롯의 과금 옵션만 추가하며, 유효 전환이 확정된 경우에만 비용을 누적한다. 누적 유효 전환 50건 달성 후에는 oCPM 전환을 안내하되 성과형 이용은 월 집행 상한 안에서 유지한다.
+    <t>최근 N개월 유상 광고 집행 이력이 없는 입점 셀러가 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯을 대상으로 순수 성과형 캠페인을 만들고 예산·기간·전환 유형을 관리하는 기능이다. 신규 지면을 만들지 않고 기존 sponsored 슬롯의 과금 옵션만 추가하며, 유효 전환이 확정된 경우에만 비용을 누적한다. 누적 유효 전환 50건 달성 후에는 oCPM 전환을 안내하되 성과형 이용은 월 집행 상한 안에서 유지한다.
 [기능의 근거] 선불 광고비와 성과 불확실성 때문에 상품광고를 시작하기 어려운 중소·신규 셀러가 성과 발생분만 비용을 내도록 지원한다.
 [성공 기준] 첫 캠페인 전환 발생률이 파일럿에서 35% 이상에 도달한다.
 [개발 준비 슬롯]
@@ -220,7 +221,7 @@
     <t>2 전환 측정 및 어트리뷰션</t>
   </si>
   <si>
-    <t xml:space="preserve">내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백으로 last-click 7일 기준의 과금 귀속 전환을 수집·검증하고, 홈 추천 피드 광고의 순증분 효과를 holdout 대조군으로 측정한다. last-click은 과금 귀속용이며 view-through는 제외한다. holdout은 광고가 없었어도 오가닉 추천으로 발생했을 전환을 제외하기 위한 증분 검증·정산 보정용으로, 과금 귀속과 구분한다.
+    <t>내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백으로 last-click 7일 기준의 과금 귀속 전환을 수집·검증하고, 홈 추천 피드 광고의 순증분 효과를 holdout 대조군으로 측정한다. last-click은 과금 귀속용이며 view-through는 제외한다. holdout은 광고가 없었어도 오가닉 추천으로 발생했을 전환을 제외하기 위한 증분 검증·정산 보정용으로, 과금 귀속과 구분한다.
 1. ○ Given 내부 구매 또는 쿠폰 사용 로그가 수신되었을 때, When 클릭 후 7일 안의 이벤트가 멱등키 중복 제거를 통과하면, Then 해당 이벤트를 마지막 유효 클릭 기준 잠정 과금 전환으로 집계한다.
 2. ○ Given 외부 광고주가 전환 API 또는 포스트백을 호출했을 때, When 필수 필드와 멱등키가 유효하면, Then 중복 없이 잠정 전환을 저장하고 수신 결과를 반환한다.
 3. ○ Given 홈 추천 피드의 성과형 캠페인이 holdout 실험 대상일 때, When 노출군과 미노출 유사 이용자군의 검증 기간 전환을 비교하면, Then 순증분 전환 수·증분 전환율·신뢰도·표본 충족 상태를 저장한다.
@@ -230,7 +231,7 @@
     <t>2.1 전환 수집 및 검증</t>
   </si>
   <si>
-    <t xml:space="preserve">홈 개인화 추천 피드 sponsored 슬롯의 내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백에서 마지막 유효 클릭 기준 과금 전환을 수집·검증하고, holdout 대조군의 순증분 전환 산정에 필요한 원천 데이터를 제공하는 기능이다. MVP에서는 클릭 기여만 과금하며 view-through 기여와 앱 설치 전환은 제외한다. last-click 7일은 과금 귀속용이고 holdout 결과는 증분 검증·정산 보정용으로 분리한다.
+    <t>홈 개인화 추천 피드 sponsored 슬롯의 내부 구매·쿠폰 사용 로그와 외부 전환 API·포스트백에서 마지막 유효 클릭 기준 과금 전환을 수집·검증하고, holdout 대조군의 순증분 전환 산정에 필요한 원천 데이터를 제공하는 기능이다. MVP에서는 클릭 기여만 과금하며 view-through 기여와 앱 설치 전환은 제외한다. last-click 7일은 과금 귀속용이고 holdout 결과는 증분 검증·정산 보정용으로 분리한다.
 [기능의 근거] 광고주는 실제 성과에만 비용을 낸다는 신뢰가 필요하고, 플랫폼은 잘못된 전환 과금과 자연전환 과대평가를 방지해야 한다.
 [성공 기준] 유효 전환율이 파일럿에서 0.15% 이상이고 전환 예측 오차가 절대오차 20% 이하를 유지한다.
 [개발 준비 슬롯]
@@ -276,7 +277,7 @@
     <t>2.2 holdout 증분성 측정</t>
   </si>
   <si>
-    <t xml:space="preserve">홈 개인화 추천 피드의 성과형 sponsored 슬롯이 오가닉 추천 대비 실제로 만든 순증분 전환을 holdout 대조군으로 측정하는 기능이다. 노출군과 광고를 노출하지 않는 유사 이용자군의 전환 차이를 산정해 수익 검증과 정산 보정에 사용한다. last-click 과금 귀속을 대체하지 않으며, 표본과 신뢰도가 부족한 결과는 자동 확대·정산 보정에서 제외한다.
+    <t>홈 개인화 추천 피드의 성과형 sponsored 슬롯이 오가닉 추천 대비 실제로 만든 순증분 전환을 holdout 대조군으로 측정하는 기능이다. 노출군과 광고를 노출하지 않는 유사 이용자군의 전환 차이를 산정해 수익 검증과 정산 보정에 사용한다. last-click 과금 귀속을 대체하지 않으며, 표본과 신뢰도가 부족한 결과는 자동 확대·정산 보정에서 제외한다.
 [기능의 근거] 발견 지면에서는 광고가 없었어도 오가닉 추천으로 발생했을 전환이 존재하므로, 과금 전환만으로 광고의 순증분 가치를 판단하면 광고 기여와 거래 수수료를 과대평가할 수 있다.
 [성공 기준] holdout 결과에서 증분 전환율이 양수이고, 표본 충족·신뢰도 기준을 만족한 캠페인 비율을 파일럿 확대 판단에 활용한다.
 [개발 준비 슬롯]
@@ -323,7 +324,7 @@
     <t>3 타겟팅·성과 예측·품질 방어</t>
   </si>
   <si>
-    <t xml:space="preserve">추천 AI의 사용자·상품 맥락별 예상 전환율과 추천 적합도를 활용해 신규 성과형 광고의 참여 자격·노출 순위·품질 방어를 결정한다. 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 성과형과 기존 oCPM은 동일 경매로 경쟁한다. 예상 eCPM·추천 적합도·품질 최소 기준에 못 미친 캠페인은 노출하지 않아 공짜 소진과 추천 경험 훼손을 방어한다.
+    <t>추천 AI의 사용자·상품 맥락별 예상 전환율과 추천 적합도를 활용해 신규 성과형 광고의 참여 자격·노출 순위·품질 방어를 결정한다. 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 성과형과 기존 oCPM은 동일 경매로 경쟁한다. 예상 eCPM·추천 적합도·품질 최소 기준에 못 미친 캠페인은 노출하지 않아 공짜 소진과 추천 경험 훼손을 방어한다.
 1. ○ Given 셀러와 상품의 최근 90일 판매·평점·재고·배송 품질 및 유상 광고 집행 이력이 있을 때, When 참여 자격을 평가하면, Then 최근 N개월 유상 광고 집행 이력이 0원인 신규 광고주 여부와 기존 품질 기준 충족 여부 및 제한 사유를 저장한다.
 2. ○ Given 홈 개인화 추천 피드 sponsored 슬롯의 경매가 발생하면, When 신규 성과형 캠페인을 평가하면, Then 추천 AI 예상 전환율×플랫폼 제시 전환 단가로 eCPM을 계산하고 추천 적합도·품질 점수를 함께 산정한다.
 3. ○ Given 신규 성과형과 기존 oCPM 캠페인이 같은 sponsored 슬롯에 참여할 때, When eCPM·추천 적합도·품질 랭킹을 산정하면, Then oCPM 바닥가 95%와 80% 가드레일을 적용해 성과형 노출 또는 oCPM 대체를 결정한다.
@@ -333,7 +334,7 @@
     <t>3.1 참여 자격 평가와 경매 품질 방어</t>
   </si>
   <si>
-    <t xml:space="preserve">추천 AI의 사용자·상품 맥락별 예상 전환율과 추천 적합도, 셀러·상품 품질을 평가해 홈 개인화 추천 피드 기존 sponsored 슬롯에서 신규 성과형 광고와 기존 oCPM 광고의 노출 순위를 결정하는 기능이다. 신규 성과형은 예상 전환율×플랫폼 제시 전환 단가의 eCPM으로 환산해 동일 경매에서 경쟁한다. 예상 eCPM·추천 적합도·품질이 최소 기준에 못 미치면 광고를 노출하지 않으며, 기존 95%·80% oCPM 바닥가 가드레일을 유지한다.
+    <t>추천 AI의 사용자·상품 맥락별 예상 전환율과 추천 적합도, 셀러·상품 품질을 평가해 홈 개인화 추천 피드 기존 sponsored 슬롯에서 신규 성과형 광고와 기존 oCPM 광고의 노출 순위를 결정하는 기능이다. 신규 성과형은 예상 전환율×플랫폼 제시 전환 단가의 eCPM으로 환산해 동일 경매에서 경쟁한다. 예상 eCPM·추천 적합도·품질이 최소 기준에 못 미치면 광고를 노출하지 않으며, 기존 95%·80% oCPM 바닥가 가드레일을 유지한다.
 [기능의 근거] 전환 가능성이 낮은 캠페인의 무료 노출 소진과 기존 oCPM 매출 기회비용을 방어해야 한다.
 [성공 기준] 공짜 소진율을 파일럿에서 15% 이하로 유지한다.
 [개발 준비 슬롯]
@@ -372,7 +373,7 @@
     <t>4 광고주 성과 대시보드</t>
   </si>
   <si>
-    <t xml:space="preserve">광고주와 운영자가 홈 추천 피드 성과형 캠페인의 과금 전환, holdout 기반 순증분 전환, 오가닉 추천 잠식, 신규 고객 획득 및 밀도·점유율을 함께 확인할 수 있게 한다. 과금 귀속 지표와 증분성 검증 지표의 목적·집계 지연·보정 상태를 명확히 구분한다. 개인 식별 정보와 holdout 대상 배정 정보는 광고주에게 노출하지 않는다.
+    <t>광고주와 운영자가 홈 추천 피드 성과형 캠페인의 과금 전환, holdout 기반 순증분 전환, 오가닉 추천 잠식, 신규 고객 획득 및 밀도·점유율을 함께 확인할 수 있게 한다. 과금 귀속 지표와 증분성 검증 지표의 목적·집계 지연·보정 상태를 명확히 구분한다. 개인 식별 정보와 holdout 대상 배정 정보는 광고주에게 노출하지 않는다.
 1. ○ Given 광고주가 권한 있는 캠페인을 조회할 때, When 기간·상품·홈 추천 피드 sponsored 슬롯·전환 유형 필터를 적용하면, Then 노출·클릭·잠정 및 확정 전환·전환당 비용·누적 비용·잔여 예산을 반환한다.
 2. ○ Given holdout 결과가 산출되었을 때, When 광고주 또는 운영자가 증분성 지표를 조회하면, Then 순증분 전환·증분 전환율·오가닉 추천 잠식률·신규 고객 획득 수와 산출 상태를 분리해 표시한다.
 3. ○ Given 전환이 발생하지 않은 기간일 때, When 성과 요약을 표시하면, Then 과금액 0원과 해당 기간의 노출·클릭·holdout 집계 상태를 구분해 표시한다.
@@ -382,7 +383,7 @@
     <t>4.1 전환 중심 성과 대시보드</t>
   </si>
   <si>
-    <t xml:space="preserve">광고주가 홈 개인화 추천 피드 sponsored 슬롯 성과형 캠페인의 노출·과금 전환·비용·예산과 holdout 기반 순증분 성과를 분리해 확인하는 기능이다. last-click 7일 과금 귀속과 holdout 증분 검증·정산 보정의 역할을 명확히 구분한다. 오가닉 추천 잠식률, 신규 고객 도달·획득 수, 광고 밀도·점유율은 광고주와 운영자 권한에 맞춰 제공한다.
+    <t>광고주가 홈 개인화 추천 피드 sponsored 슬롯 성과형 캠페인의 노출·과금 전환·비용·예산과 holdout 기반 순증분 성과를 분리해 확인하는 기능이다. last-click 7일 과금 귀속과 holdout 증분 검증·정산 보정의 역할을 명확히 구분한다. 오가닉 추천 잠식률, 신규 고객 도달·획득 수, 광고 밀도·점유율은 광고주와 운영자 권한에 맞춰 제공한다.
 [기능의 근거] 광고주는 성과와 비용 산정 근거를 이해해야 재집행할 수 있다.
 [성공 기준] 파일럿 30일 재집행률이 30% 이상에 도달한다.
 [개발 준비 슬롯]
@@ -415,7 +416,7 @@
     <t>5 플랫폼 운영·정산·보장 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">관리자가 홈 개인화 추천 피드의 sponsored 슬롯, 광고 밀도 캡, 추천 적합도 기준, holdout 실험, 전환 검증과 정산 보정을 운영할 수 있게 한다. 신규 성과형과 기존 oCPM의 동일 경매 구조 및 기존 지면 매출 유지율을 관리한다. 고정 전환 건수 보장은 포함하지 않으며, 유효 전환 발생분만 과금하는 순수 성과형 원칙을 유지한다.
+    <t>관리자가 홈 개인화 추천 피드의 sponsored 슬롯, 광고 밀도 캡, 추천 적합도 기준, holdout 실험, 전환 검증과 정산 보정을 운영할 수 있게 한다. 신규 성과형과 기존 oCPM의 동일 경매 구조 및 기존 지면 매출 유지율을 관리한다. 고정 전환 건수 보장은 포함하지 않으며, 유효 전환 발생분만 과금하는 순수 성과형 원칙을 유지한다.
 1. ○ Given 관리자가 파일럿 운영 권한을 보유할 때, When 홈 추천 피드 sponsored 슬롯·추천 N개당 광고 1개 밀도 캡·셀러 등급·예산·노출 한도를 설정하면, Then 변경 값과 변경자를 감사 로그에 저장한다.
 2. ○ Given holdout 실험이 실행 중일 때, When 관리자가 실험군·대조군·표본 충족·결과 지연을 검토하면, Then 실험 상태와 정산 보정 적용 여부를 기록한다.
 3. ○ Given 공짜 소진율·증분 전환율·오가닉 추천 잠식률·광고 점유율·지면 매출 유지율이 파일럿 기준을 벗어났을 때, When 가드레일 평가가 실행되면, Then 성과형 노출 한도를 축소하거나 신규 유입을 중단한다.
@@ -425,7 +426,7 @@
     <t>5.1 파일럿 운영·검증·정산 콘솔</t>
   </si>
   <si>
-    <t xml:space="preserve">관리자가 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 참여 자격, 추천 적합도·밀도 캡, holdout 실험, 전환 검증, 증분성 정산 보정 및 수익 가드레일을 운영하는 기능이다. 신규 성과형과 기존 oCPM의 동일 경매·별도 과금 방식을 함께 관리한다. 대형 브랜드 CPD는 별도 상품으로 유지한다.
+    <t>관리자가 홈 개인화 추천 피드의 기존 sponsored 슬롯에서 참여 자격, 추천 적합도·밀도 캡, holdout 실험, 전환 검증, 증분성 정산 보정 및 수익 가드레일을 운영하는 기능이다. 신규 성과형과 기존 oCPM의 동일 경매·별도 과금 방식을 함께 관리한다. 대형 브랜드 CPD는 별도 상품으로 유지한다.
 [기능의 근거] 순수 성과형 과금의 신뢰성과 기존 지면 수익 방어를 동시에 운영해야 한다.
 [성공 기준] 지면 매출 유지율을 기존 oCPM 대비 95% 이상으로 유지한다.
 [개발 준비 슬롯]
@@ -465,7 +466,7 @@
     <t>6 단계적 출시 및 확장 로드맵</t>
   </si>
   <si>
-    <t xml:space="preserve">홈 개인화 추천 피드의 기존 sponsored 슬롯에서 제한된 신규 광고주 성과형 파일럿을 운영하고, 증분성·오가닉 보호·지면 수익을 함께 검증한 뒤 확대 여부를 결정한다. MVP는 기존 슬롯의 과금 옵션 추가 범위로 한정한다. 추가 지면, 외부 미입점 광고주, 목표 CPA 입찰과 CPA 보장은 Phase 2 이후 후보로 관리한다.
+    <t>홈 개인화 추천 피드의 기존 sponsored 슬롯에서 제한된 신규 광고주 성과형 파일럿을 운영하고, 증분성·오가닉 보호·지면 수익을 함께 검증한 뒤 확대 여부를 결정한다. MVP는 기존 슬롯의 과금 옵션 추가 범위로 한정한다. 추가 지면, 외부 미입점 광고주, 목표 CPA 입찰과 CPA 보장은 Phase 2 이후 후보로 관리한다.
 1. ○ Given 파일럿 출시를 준비할 때, When 홈 개인화 추천 피드 sponsored 슬롯·광고 밀도 캡·holdout 설계·대상 셀러 수·기간·핵심 지표 임계값을 등록하면, Then 승인 전에는 집행을 시작할 수 없다.
 2. ○ Given 파일럿 평가 기간이 종료되었을 때, When 성장·수익성·증분성·오가닉 보호·건전성 지표를 산출하면, Then 확대·유지·축소·중단 중 하나의 결정을 기록한다.
 3. ○ Given 공짜 소진율이 20%를 초과하거나 지면 매출 유지율이 90% 미만이거나 오가닉 추천 잠식률이 목표를 초과할 때, When 축소·중단 규칙이 평가되면, Then 신규 성과형 캠페인 유입을 중단하거나 추천 피드 점유율을 축소한다.
@@ -478,7 +479,7 @@
     <t>6.1 파일럿 게이트와 단계적 확대 관리</t>
   </si>
   <si>
-    <t xml:space="preserve">홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 광고주 성과형 파일럿을 운영하고, 증분성·오가닉 보호·지면 수익을 기준으로 확대·유지·축소·중단을 결정하는 기능이다. MVP는 기존 슬롯의 과금 옵션 추가로 한정한다. 추가 발견 지면과 외부 미입점 광고주, 목표 CPA 입찰은 holdout 검증 후 Phase 2 후보로 관리한다.
+    <t>홈 개인화 추천 피드의 기존 sponsored 슬롯에서 신규 광고주 성과형 파일럿을 운영하고, 증분성·오가닉 보호·지면 수익을 기준으로 확대·유지·축소·중단을 결정하는 기능이다. MVP는 기존 슬롯의 과금 옵션 추가로 한정한다. 추가 발견 지면과 외부 미입점 광고주, 목표 CPA 입찰은 holdout 검증 후 Phase 2 후보로 관리한다.
 [기능의 근거] 제한된 파일럿에서 수익성과 건전성을 검증한 뒤 안전하게 대상 카테고리와 셀러를 확대해야 한다.
 [성공 기준] 신규 성과형 광고주 수 300명과 성과형 광고 매출 비중 5% 이상을 달성한다.
 [개발 준비 슬롯]
@@ -527,7 +528,7 @@
     <t>전환 단가 책정 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">단가 대안 비교: | 안 | 산정 방식 | 장점 | 한계 | MVP 적합성 |
+    <t>단가 대안 비교: | 안 | 산정 방식 | 장점 | 한계 | MVP 적합성 |
 |---|---|---|---|---|
 | 고정 단가 | 플랫폼이 예상 전환율·원가로 단가를 제시한다. | 신규 셀러가 쉽게 시작할 수 있다. | 시장 수요와 상품별 차이를 반영하기 어렵다. | 보통이다. |
 | 목표 CPA 입찰 | 광고주가 희망 전환 단가를 입찰한다. | 광고주가 가격을 통제할 수 있다. | 신규 셀러의 입찰 난도가 높고 저가 입찰이 인벤토리 품질을 훼손할 수 있다. | 낮음이다. |
@@ -551,7 +552,7 @@
     <t>상품광고 경매 및 노출 배분 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">MVP·Phase 2 노출 경쟁 구조: - MVP 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯이다.
+    <t>MVP·Phase 2 노출 경쟁 구조: - MVP 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯이다.
 - MVP는 신규 지면 개발이 아니라 기존 sponsored 슬롯에 신규 광고주 한정 전환 성과형 과금 옵션을 추가한다.
 - 신규 성과형과 기존 oCPM은 같은 sponsored 슬롯에서 동일 경매로 경쟁한다.
 - MVP에서 광고주는 전환 단가를 입찰하지 않고 플랫폼이 카테고리 기준단가를 제시한다.
@@ -572,7 +573,7 @@
     <t>전환 확정 및 정산 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">검증·정산 주기: - 내부 구매·쿠폰 사용 전환은 발생일 기준으로 잠정 집계하고 D+7에 유효 여부를 확정한다.
+    <t>검증·정산 주기: - 내부 구매·쿠폰 사용 전환은 발생일 기준으로 잠정 집계하고 D+7에 유효 여부를 확정한다.
 - 외부 전환은 광고주 포스트백 또는 전환 API 수신 후 잠정 집계하고 D+14에 유효 여부를 확정한다.
 - holdout 증분성 결과는 전환 확정 데이터가 집계된 뒤 산출하며, 표본과 신뢰도 기준 충족 시에만 정산 보정 후보로 사용한다.
 - 확정 전환 비용은 매일 누적 표시하고 광고주 청구서는 매월 1일~말일 확정분을 기준으로 다음 달 5일 발행한다.
@@ -597,7 +598,7 @@
     <t>성과형 상품광고 GTM 및 온보딩 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">파일럿 대상·지면: - 파일럿 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯이다.
+    <t>파일럿 대상·지면: - 파일럿 지면은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’의 기존 광고(sponsored) 슬롯이다.
 - MVP는 신규 지면이 아니라 기존 sponsored 슬롯의 신규 광고주 한정 전환 성과형 과금 옵션이다.
 - MVP 대상은 최근 N개월 유상 광고 집행 이력이 0원인 입점 신규 광고주이며 별도 매출·거래액 증빙 서류는 요구하지 않는다.
 - 초기 초대 대상은 최근 90일 주문 30건 이상, 상품 평점 4.2점 이상, 품절률 5% 이하 및 배송 품질 기준을 충족한 셀러다.
@@ -623,7 +624,7 @@
     <t>성과형 상품광고 공통 기술 명세</t>
   </si>
   <si>
-    <t xml:space="preserve">[공통 정의]
+    <t>[공통 정의]
 용어 정의: - 기존 sponsored 슬롯은 홈 개인화 추천 피드 ‘○○님을 위한 추천 상품’ 안에서 기존 oCPM 광고가 노출되는 광고 슬롯이다.
 - 신규 성과형은 신규 광고주에게 유효 전환 시에만 비용을 청구하는 기존 sponsored 슬롯의 과금 옵션이다.
 - eCPM은 추천 AI 예상 전환율×전환 단가×1,000으로 계산하는 신규 성과형의 경매 비교값이다.
@@ -673,7 +674,7 @@
     <t>신규 광고주 참여 및 졸업 정책</t>
   </si>
   <si>
-    <t xml:space="preserve">신규 광고주 정의: - 신규 광고주는 최근 N개월 유상 광고 집행 이력이 0원인 입점 셀러이다.
+    <t>신규 광고주 정의: - 신규 광고주는 최근 N개월 유상 광고 집행 이력이 0원인 입점 셀러이다.
 - 유상 광고 집행 이력은 에이블리 기존 신규 광고주·무상 광고비 판정과 동일한 내부 광고 집행 이력 기준으로 판단한다.
 - 신규 광고주 판정에는 별도 매출·거래액 증빙 서류를 요구하지 않는다.
 - 유상 광고 집행 이력 플래그는 해당 없음, 소액, 일반 중 하나로 저장한다.
@@ -696,66 +697,114 @@
 - 초대·온보딩 운영은 성과형 상품광고 GTM 및 온보딩 정책을 우선 적용한다.
 MVP 성과형 상품광고의 신규 광고주 판정, 성과 검증 후 oCPM 전환 안내 및 집행 상한을 정한다. 전환 단가·경매·전환 확정·정산·GTM 세부 규칙은 기존 정책을 우선 적용한다.</t>
   </si>
+  <si>
+    <t>윤지욱</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="30"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF595959"/>
-      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
       <color rgb="FF9900FF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="FF666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="FF9900FF"/>
-      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF9900FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FFFBBC04"/>
-      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -767,12 +816,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFefefef"/>
+        <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf5f5f5"/>
+        <fgColor rgb="FFF5F5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -803,7 +852,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFd9d9d9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -840,7 +889,7 @@
         <color rgb="FFB7B7B7"/>
       </top>
       <bottom style="hair">
-        <color rgb="FFe8e8e8"/>
+        <color rgb="FFE8E8E8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -851,7 +900,7 @@
         <color rgb="FFB7B7B7"/>
       </top>
       <bottom style="hair">
-        <color rgb="FFe8e8e8"/>
+        <color rgb="FFE8E8E8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -862,7 +911,7 @@
       </right>
       <top/>
       <bottom style="hair">
-        <color rgb="FFe8e8e8"/>
+        <color rgb="FFE8E8E8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -871,7 +920,7 @@
       <right/>
       <top/>
       <bottom style="hair">
-        <color rgb="FFe8e8e8"/>
+        <color rgb="FFE8E8E8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -881,17 +930,8 @@
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -944,9 +984,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1282,12 +1331,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:J42"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="15"/>
+  <sheetFormatPr defaultColWidth="15" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="4" width="25" customWidth="1"/>
@@ -1298,557 +1347,558 @@
     <col min="10" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:7" ht="45" x14ac:dyDescent="0.3">
+      <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="24"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="24"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="24"/>
+    </row>
+    <row r="10" spans="2:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="B10" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+    </row>
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+    </row>
+    <row r="13" spans="2:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+    </row>
+    <row r="14" spans="2:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+    </row>
+    <row r="15" spans="2:7" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+    </row>
+    <row r="16" spans="2:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" ht="99.00000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+    </row>
+    <row r="17" spans="2:10" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+    </row>
+    <row r="18" spans="2:10" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" ht="79.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+    </row>
+    <row r="19" spans="2:10" ht="118.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" ht="118.80000000000001" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+    </row>
+    <row r="20" spans="2:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="673.2" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+    </row>
+    <row r="21" spans="2:10" ht="198" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" ht="198.00000000000003" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+    </row>
+    <row r="22" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+    </row>
+    <row r="23" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+    </row>
+    <row r="24" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+    </row>
+    <row r="27" spans="2:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="B27" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+    </row>
+    <row r="29" spans="2:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="29" ht="25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="J29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J29" s="6" t="s">
+    </row>
+    <row r="30" spans="2:10" ht="156" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="G30" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B31" s="11"/>
+      <c r="C31" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="13"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="14"/>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="11"/>
+      <c r="E31" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="16" t="s">
+      <c r="F31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H31" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="I31" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" s="17"/>
+    </row>
+    <row r="32" spans="2:10" ht="168" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G31" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="9" t="s">
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B33" s="11"/>
+      <c r="C33" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="D33" s="11"/>
+      <c r="E33" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="13"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="14"/>
-      <c r="C33" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="16" t="s">
+      <c r="H33" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="I33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="17"/>
+    </row>
+    <row r="34" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B34" s="11"/>
+      <c r="C34" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J34" s="17"/>
+    </row>
+    <row r="35" spans="2:10" ht="180" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33" s="19" t="s">
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B36" s="11"/>
+      <c r="C36" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J33" s="20"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="14"/>
-      <c r="C34" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="17" t="s">
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="2:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B38" s="11"/>
+      <c r="C38" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G35" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="13"/>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="14"/>
-      <c r="C36" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" s="17" t="s">
+      <c r="H38" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="17"/>
+    </row>
+    <row r="39" spans="2:10" ht="168" x14ac:dyDescent="0.3">
+      <c r="B39" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G36" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J36" s="20"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="10" t="s">
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B40" s="11"/>
+      <c r="C40" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="14"/>
-      <c r="C38" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" s="17" t="s">
+      <c r="H40" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="2:10" ht="168" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I38" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="20"/>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="10" t="s">
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="2:10" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B42" s="11"/>
+      <c r="C42" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G42" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G39" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="13"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="14"/>
-      <c r="C40" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J40" s="20"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="13"/>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="14"/>
-      <c r="C42" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="16" t="s">
+      <c r="H42" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F42" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="J42" s="20"/>
+      <c r="I42" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J42" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="B27:G27"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:D8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="15"/>
+  <sheetFormatPr defaultColWidth="15" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1856,85 +1906,86 @@
     <col min="4" max="4" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+    <row r="2" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="24" t="s">
+    </row>
+    <row r="3" spans="2:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>82</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="25" t="s">
+    </row>
+    <row r="4" spans="2:4" ht="313.5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>85</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="25" t="s">
+    </row>
+    <row r="5" spans="2:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>88</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="25" t="s">
+    </row>
+    <row r="6" spans="2:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>91</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="25" t="s">
+    </row>
+    <row r="7" spans="2:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>94</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="25" t="s">
+    </row>
+    <row r="8" spans="2:4" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>97</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="25" t="s">
-        <v>99</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>